--- a/outputs/sport-booking-agile-project-tracker.xlsx
+++ b/outputs/sport-booking-agile-project-tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Documents/Personal/Personal Project/Sport Booking WebApp/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18577964-A7D2-044C-9473-37BC493643ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F96A9E9-947A-BC4E-BF3D-683CD1EB1492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Usage Guide" sheetId="1" r:id="rId1"/>
@@ -24,9 +24,9 @@
     <sheet name="Lookups" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Product Backlog'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Product Backlog'!$A$1:$K$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Release Checklist'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sprint Board'!$A$1:$K$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sprint Board'!$A$1:$N$135</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="876">
   <si>
     <t>Hướng Dẫn Sử Dụng Agile Tracker - Sport Booking WebApp</t>
   </si>
@@ -2584,6 +2584,96 @@
   </si>
   <si>
     <t>Document browse, login, booking, vendor and admin checks</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Pull Request #2</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/01c38b7f05e22696d4da7daecdea6255d82aa7ef</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/1dc61b5806dd82d6278b16a77a670b1f2fafabaf</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/68c7c7265f0f6bc84cbeba6ad132d0d5319c64a5</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/e7f1cb3884c70e2631e7a305d47345e81d2386d5</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/9ea6710c55bd5d75ce992ff74a9f8bc98e625ef7</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/ee452ebe7b0fe9bfb4b1f96c2503a23e0b9919da</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/pull/3</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/a818783bc763e7894935b42c8907eccd84469495</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/0d1e65b2fe457df87125e1bd07cff1118089506a</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/60c9e93ddd889fcf46afe0d050f85426039e38dd</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/ccc1d90b863917fa4444e3b3ed4a854c616c2da7</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/7c28081b592376b5f114320c4b2b97ab7aaafcf5</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/e970e163b1498ea48bb2a978c79ec2acc64e7493</t>
+  </si>
+  <si>
+    <t>Members</t>
+  </si>
+  <si>
+    <t>Dương Quốc Hiếu</t>
+  </si>
+  <si>
+    <t>Assignee</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>SB-030 covered by SB-005 commit</t>
+  </si>
+  <si>
+    <t>SB-031, SB-032 covered by SB-006 commit</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/505a5b2f4106a5681a9ae6920cd5f6778a43d28d</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/6517f94dc54d956f2018cd3c7d5b40d10c88a7b4</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/e94d389dd5612f0c5334dca9f1a32a2ebfc7b484</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/8450c708a287d7cceee8b9bbb48f2c7408861838</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/e56525bdc2a817c2e3725ffb2161949b3d2e3bd0</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/f3874dedaafd79fa41468d446b09b3fcd230fcd8</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/8bfc111035aaeb6c025965253ca1464c2e08cf13</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/7bc4b76e12b9605a57605e02dad7bdf814952e71</t>
+  </si>
+  <si>
+    <t>https://github.com/dqhieuse/sport_booking_webapp/commit/112c524ea170bd378a723c8489e3022b4ac2505a</t>
   </si>
 </sst>
 </file>
@@ -2593,7 +2683,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -2642,20 +2732,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF1F2937"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="16"/>
       <color theme="3" tint="0.89992980742820516"/>
       <name val="Aptos"/>
@@ -2664,6 +2740,30 @@
       <b/>
       <sz val="11"/>
       <color theme="3" tint="0.89996032593768116"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F2937"/>
       <name val="Aptos"/>
     </font>
   </fonts>
@@ -2801,10 +2901,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2886,76 +2987,44 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="12">
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="3" tint="9.9948118533890809E-2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEAE8FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor theme="2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3001,21 +3070,18 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color theme="3" tint="9.9948118533890809E-2"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
+          <bgColor theme="2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3041,28 +3107,31 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF7030A0"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFEAE8FF"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF7030A0"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFEAE8FF"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor theme="2"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3976,14 +4045,14 @@
       <c r="L21" s="6"/>
     </row>
     <row r="22" spans="1:12" ht="29.75" customHeight="1">
-      <c r="A22" s="35"/>
-      <c r="B22" s="35" t="s">
+      <c r="A22" s="38"/>
+      <c r="B22" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
@@ -4005,22 +4074,22 @@
       <c r="L23" s="6"/>
     </row>
     <row r="24" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A24" s="33" t="s">
+      <c r="A24" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="33" t="s">
+      <c r="C24" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="33" t="s">
+      <c r="D24" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="E24" s="33" t="s">
+      <c r="E24" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="33" t="s">
+      <c r="F24" s="40" t="s">
         <v>89</v>
       </c>
       <c r="G24" s="6"/>
@@ -4031,22 +4100,22 @@
       <c r="L24" s="6"/>
     </row>
     <row r="25" spans="1:12" ht="42.75" customHeight="1">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="9" t="s">
         <v>94</v>
       </c>
       <c r="G25" s="6"/>
@@ -4057,22 +4126,22 @@
       <c r="L25" s="6"/>
     </row>
     <row r="26" spans="1:12" ht="42.75" customHeight="1">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="9" t="s">
         <v>99</v>
       </c>
       <c r="G26" s="6"/>
@@ -4096,14 +4165,14 @@
       <c r="L27" s="6"/>
     </row>
     <row r="28" spans="1:12" ht="29.75" customHeight="1">
-      <c r="A28" s="34"/>
-      <c r="B28" s="35" t="s">
+      <c r="A28" s="39"/>
+      <c r="B28" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -4125,22 +4194,22 @@
       <c r="L29" s="6"/>
     </row>
     <row r="30" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A30" s="33" t="s">
+      <c r="A30" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B30" s="33" t="s">
+      <c r="B30" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="33" t="s">
+      <c r="D30" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="33" t="s">
+      <c r="E30" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="F30" s="33" t="s">
+      <c r="F30" s="40" t="s">
         <v>103</v>
       </c>
       <c r="G30" s="6"/>
@@ -4151,22 +4220,22 @@
       <c r="L30" s="6"/>
     </row>
     <row r="31" spans="1:12" ht="42.75" customHeight="1">
-      <c r="A31" s="2">
+      <c r="A31" s="9">
         <v>1</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="9" t="s">
         <v>108</v>
       </c>
       <c r="G31" s="6"/>
@@ -4177,22 +4246,22 @@
       <c r="L31" s="6"/>
     </row>
     <row r="32" spans="1:12" ht="42.75" customHeight="1">
-      <c r="A32" s="2">
+      <c r="A32" s="9">
         <v>2</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="9" t="s">
         <v>113</v>
       </c>
       <c r="G32" s="6"/>
@@ -4203,22 +4272,22 @@
       <c r="L32" s="6"/>
     </row>
     <row r="33" spans="1:12" ht="64" customHeight="1">
-      <c r="A33" s="2">
+      <c r="A33" s="9">
         <v>3</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="9" t="s">
         <v>118</v>
       </c>
       <c r="G33" s="6"/>
@@ -4229,22 +4298,22 @@
       <c r="L33" s="6"/>
     </row>
     <row r="34" spans="1:12" ht="42.75" customHeight="1">
-      <c r="A34" s="2">
+      <c r="A34" s="9">
         <v>4</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="9" t="s">
         <v>123</v>
       </c>
       <c r="G34" s="6"/>
@@ -4255,22 +4324,22 @@
       <c r="L34" s="6"/>
     </row>
     <row r="35" spans="1:12" ht="42.75" customHeight="1">
-      <c r="A35" s="2">
+      <c r="A35" s="9">
         <v>5</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="9" t="s">
         <v>128</v>
       </c>
       <c r="G35" s="6"/>
@@ -4281,22 +4350,22 @@
       <c r="L35" s="6"/>
     </row>
     <row r="36" spans="1:12" ht="64" customHeight="1">
-      <c r="A36" s="2">
+      <c r="A36" s="9">
         <v>6</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="9" t="s">
         <v>132</v>
       </c>
       <c r="G36" s="6"/>
@@ -6439,6 +6508,7 @@
       <c r="L200" s="6"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6460,7 +6530,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="45.25" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>133</v>
       </c>
       <c r="B1" s="5"/>
@@ -6537,7 +6607,7 @@
       </c>
       <c r="G4" s="9" t="str">
         <f>'Sprint Plan'!H2</f>
-        <v>In Progress</v>
+        <v>Done</v>
       </c>
       <c r="H4" s="9" t="str">
         <f>'Sprint Plan'!F2</f>
@@ -6553,7 +6623,7 @@
       </c>
       <c r="B5" s="21">
         <f>COUNTIF('Product Backlog'!G2:G200,"Done")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="9" t="str">
@@ -6570,7 +6640,7 @@
       </c>
       <c r="G5" s="9" t="str">
         <f>'Sprint Plan'!H3</f>
-        <v>Planned</v>
+        <v>Done</v>
       </c>
       <c r="H5" s="9" t="str">
         <f>'Sprint Plan'!F3</f>
@@ -6652,7 +6722,7 @@
       </c>
       <c r="B8" s="21" t="str">
         <f>COUNTIF('Release Checklist'!D2:D100,"Done")&amp;"/"&amp;COUNTA('Release Checklist'!A2:A100)</f>
-        <v>0/14</v>
+        <v>1/14</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="9" t="str">
@@ -9267,6 +9337,7 @@
       <c r="K200" s="6"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -9274,6 +9345,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
@@ -9283,7 +9355,7 @@
     <col min="4" max="4" width="8.83203125" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" customWidth="1"/>
     <col min="8" max="8" width="9.33203125" customWidth="1"/>
     <col min="9" max="9" width="15.1640625" customWidth="1"/>
     <col min="10" max="10" width="44.33203125" customWidth="1"/>
@@ -9325,7 +9397,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="21" customHeight="1">
+    <row r="2" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>170</v>
       </c>
@@ -9345,7 +9417,7 @@
         <v>175</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>176</v>
@@ -9358,7 +9430,7 @@
       </c>
       <c r="K2" s="9"/>
     </row>
-    <row r="3" spans="1:11" ht="21" customHeight="1">
+    <row r="3" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>178</v>
       </c>
@@ -9378,7 +9450,7 @@
         <v>175</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>176</v>
@@ -9391,7 +9463,7 @@
       </c>
       <c r="K3" s="9"/>
     </row>
-    <row r="4" spans="1:11" ht="21" customHeight="1">
+    <row r="4" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>182</v>
       </c>
@@ -9411,7 +9483,7 @@
         <v>175</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>176</v>
@@ -9426,7 +9498,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="21" customHeight="1">
+    <row r="5" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A5" s="9" t="s">
         <v>186</v>
       </c>
@@ -9446,7 +9518,7 @@
         <v>175</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>176</v>
@@ -9479,7 +9551,7 @@
         <v>192</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>176</v>
@@ -9512,7 +9584,7 @@
         <v>192</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>176</v>
@@ -9545,7 +9617,7 @@
         <v>192</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>176</v>
@@ -9578,7 +9650,7 @@
         <v>192</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>176</v>
@@ -9591,7 +9663,7 @@
       </c>
       <c r="K9" s="9"/>
     </row>
-    <row r="10" spans="1:11" ht="21" customHeight="1">
+    <row r="10" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>203</v>
       </c>
@@ -9624,7 +9696,7 @@
       </c>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:11" ht="21" customHeight="1">
+    <row r="11" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>209</v>
       </c>
@@ -9657,7 +9729,7 @@
       </c>
       <c r="K11" s="9"/>
     </row>
-    <row r="12" spans="1:11" ht="21" customHeight="1">
+    <row r="12" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>212</v>
       </c>
@@ -9690,7 +9762,7 @@
       </c>
       <c r="K12" s="9"/>
     </row>
-    <row r="13" spans="1:11" ht="21" customHeight="1">
+    <row r="13" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A13" s="9" t="s">
         <v>215</v>
       </c>
@@ -9723,7 +9795,7 @@
       </c>
       <c r="K13" s="9"/>
     </row>
-    <row r="14" spans="1:11" ht="21" customHeight="1">
+    <row r="14" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A14" s="9" t="s">
         <v>218</v>
       </c>
@@ -9756,7 +9828,7 @@
       </c>
       <c r="K14" s="9"/>
     </row>
-    <row r="15" spans="1:11" ht="21" customHeight="1">
+    <row r="15" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>224</v>
       </c>
@@ -9789,7 +9861,7 @@
       </c>
       <c r="K15" s="9"/>
     </row>
-    <row r="16" spans="1:11" ht="21" customHeight="1">
+    <row r="16" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A16" s="9" t="s">
         <v>227</v>
       </c>
@@ -9822,7 +9894,7 @@
       </c>
       <c r="K16" s="9"/>
     </row>
-    <row r="17" spans="1:11" ht="21" customHeight="1">
+    <row r="17" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A17" s="9" t="s">
         <v>230</v>
       </c>
@@ -9855,7 +9927,7 @@
       </c>
       <c r="K17" s="9"/>
     </row>
-    <row r="18" spans="1:11" ht="21" customHeight="1">
+    <row r="18" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A18" s="9" t="s">
         <v>233</v>
       </c>
@@ -9888,7 +9960,7 @@
       </c>
       <c r="K18" s="9"/>
     </row>
-    <row r="19" spans="1:11" ht="21" customHeight="1">
+    <row r="19" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A19" s="9" t="s">
         <v>236</v>
       </c>
@@ -9896,7 +9968,7 @@
         <v>237</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>206</v>
@@ -9914,14 +9986,14 @@
         <v>176</v>
       </c>
       <c r="I19" s="9">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K19" s="9"/>
     </row>
-    <row r="20" spans="1:11" ht="21" customHeight="1">
+    <row r="20" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A20" s="9" t="s">
         <v>241</v>
       </c>
@@ -9929,7 +10001,7 @@
         <v>237</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>206</v>
@@ -9947,14 +10019,14 @@
         <v>176</v>
       </c>
       <c r="I20" s="9">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="K20" s="9"/>
     </row>
-    <row r="21" spans="1:11" ht="21" customHeight="1">
+    <row r="21" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A21" s="9" t="s">
         <v>244</v>
       </c>
@@ -9987,7 +10059,7 @@
       </c>
       <c r="K21" s="9"/>
     </row>
-    <row r="22" spans="1:11" ht="21" customHeight="1">
+    <row r="22" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A22" s="9" t="s">
         <v>247</v>
       </c>
@@ -10020,7 +10092,7 @@
       </c>
       <c r="K22" s="9"/>
     </row>
-    <row r="23" spans="1:11" ht="21" customHeight="1">
+    <row r="23" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A23" s="9" t="s">
         <v>250</v>
       </c>
@@ -10053,7 +10125,7 @@
       </c>
       <c r="K23" s="9"/>
     </row>
-    <row r="24" spans="1:11" ht="21" customHeight="1">
+    <row r="24" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A24" s="9" t="s">
         <v>253</v>
       </c>
@@ -10086,7 +10158,7 @@
       </c>
       <c r="K24" s="9"/>
     </row>
-    <row r="25" spans="1:11" ht="21" customHeight="1">
+    <row r="25" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A25" s="9" t="s">
         <v>258</v>
       </c>
@@ -10119,7 +10191,7 @@
       </c>
       <c r="K25" s="9"/>
     </row>
-    <row r="26" spans="1:11" ht="21" customHeight="1">
+    <row r="26" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A26" s="9" t="s">
         <v>261</v>
       </c>
@@ -10152,7 +10224,7 @@
       </c>
       <c r="K26" s="9"/>
     </row>
-    <row r="27" spans="1:11" ht="21" customHeight="1">
+    <row r="27" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A27" s="9" t="s">
         <v>264</v>
       </c>
@@ -10185,7 +10257,7 @@
       </c>
       <c r="K27" s="9"/>
     </row>
-    <row r="28" spans="1:11" ht="21" customHeight="1">
+    <row r="28" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A28" s="9" t="s">
         <v>269</v>
       </c>
@@ -10218,7 +10290,7 @@
       </c>
       <c r="K28" s="9"/>
     </row>
-    <row r="29" spans="1:11" ht="21" customHeight="1">
+    <row r="29" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A29" s="9" t="s">
         <v>272</v>
       </c>
@@ -10251,7 +10323,7 @@
       </c>
       <c r="K29" s="9"/>
     </row>
-    <row r="30" spans="1:11" ht="21" customHeight="1">
+    <row r="30" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>275</v>
       </c>
@@ -10284,7 +10356,7 @@
       </c>
       <c r="K30" s="9"/>
     </row>
-    <row r="31" spans="1:11" ht="21" customHeight="1">
+    <row r="31" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A31" s="9" t="s">
         <v>278</v>
       </c>
@@ -10319,7 +10391,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="21" customHeight="1">
+    <row r="32" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>284</v>
       </c>
@@ -10352,7 +10424,7 @@
       </c>
       <c r="K32" s="9"/>
     </row>
-    <row r="33" spans="1:11" ht="21" customHeight="1">
+    <row r="33" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A33" s="9" t="s">
         <v>288</v>
       </c>
@@ -10385,7 +10457,7 @@
       </c>
       <c r="K33" s="9"/>
     </row>
-    <row r="34" spans="1:11" ht="21" customHeight="1">
+    <row r="34" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>291</v>
       </c>
@@ -10418,7 +10490,7 @@
       </c>
       <c r="K34" s="9"/>
     </row>
-    <row r="35" spans="1:11" ht="21" customHeight="1">
+    <row r="35" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A35" s="9" t="s">
         <v>297</v>
       </c>
@@ -10451,7 +10523,7 @@
       </c>
       <c r="K35" s="9"/>
     </row>
-    <row r="36" spans="1:11" ht="21" customHeight="1">
+    <row r="36" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A36" s="9" t="s">
         <v>300</v>
       </c>
@@ -10484,7 +10556,7 @@
       </c>
       <c r="K36" s="9"/>
     </row>
-    <row r="37" spans="1:11" ht="21" customHeight="1">
+    <row r="37" spans="1:11" ht="21" hidden="1" customHeight="1">
       <c r="A37" s="9" t="s">
         <v>304</v>
       </c>
@@ -12637,23 +12709,113 @@
       <c r="K200" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A1:K37" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="Sprint 1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="E2:E200" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E20 E21:E200" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Must,Should,Could,Won't"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G200" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G20 G21:G200" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Backlog,Ready,To Do,In Progress,Review,Done,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H200" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H20 H21:H200" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"Developer,Product Owner,Tester,Designer,DevOps"</formula1>
     </dataValidation>
-    <dataValidation type="whole" sqref="I2:I200" xr:uid="{00000000-0002-0000-0200-000003000000}">
+    <dataValidation type="whole" sqref="I2:I20 I21:I200" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>0</formula1>
       <formula2>40</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{1CB2216C-E35A-604C-997E-FC0A6A06C93D}">
+            <xm:f>Lookups!$A$8</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{CAB45EB1-1DFF-F047-B52A-34CE18965BF9}">
+            <xm:f>Lookups!$A$7</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{29692A7E-0A1D-3D4F-A7CB-5B53885CF602}">
+            <xm:f>Lookups!$A$6</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFEB9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{5BDA97DC-4394-3542-96D6-7BB6A0A936AC}">
+            <xm:f>Lookups!$A$5</xm:f>
+            <x14:dxf>
+              <font>
+                <color theme="3" tint="9.9948118533890809E-2"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="3" tint="0.89996032593768116"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{645E7781-27D9-B74B-804D-DEC7ABEC8832}">
+            <xm:f>Lookups!$A$3</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF7030A0"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFEAE8FF"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{D4212B82-8AC9-C54C-AEF7-7B36365749F6}">
+            <xm:f>Lookups!$A$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G2:G37</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -12710,9 +12872,11 @@
         <v>311</v>
       </c>
       <c r="C2" s="25">
+        <v>46163</v>
+      </c>
+      <c r="D2" s="25">
         <v>46164</v>
       </c>
-      <c r="D2" s="25"/>
       <c r="E2" s="9" t="s">
         <v>312</v>
       </c>
@@ -12723,7 +12887,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
@@ -12736,8 +12900,12 @@
       <c r="B3" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
+      <c r="C3" s="25">
+        <v>46164</v>
+      </c>
+      <c r="D3" s="25">
+        <v>46165</v>
+      </c>
       <c r="E3" s="9" t="s">
         <v>315</v>
       </c>
@@ -12748,7 +12916,7 @@
         <v>32</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>317</v>
+        <v>78</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
@@ -15412,7 +15580,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:K200"/>
+  <dimension ref="A1:N480"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.1640625" customWidth="1"/>
@@ -15421,14 +15589,17 @@
     <col min="4" max="4" width="8.83203125" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
     <col min="6" max="6" width="11.6640625" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" customWidth="1"/>
-    <col min="8" max="8" width="3.5" style="31" customWidth="1"/>
-    <col min="9" max="9" width="9.5" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" customWidth="1"/>
+    <col min="9" max="9" width="3.5" style="31" customWidth="1"/>
+    <col min="10" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="11" width="40.6640625" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="14.5" customWidth="1"/>
+    <col min="14" max="14" width="13.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1">
+    <row r="1" spans="1:14" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>160</v>
       </c>
@@ -15448,22 +15619,31 @@
         <v>24</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="K1" s="37" t="s">
+      <c r="L1" s="34" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="20" customHeight="1">
+      <c r="M1" s="34" t="s">
+        <v>864</v>
+      </c>
+      <c r="N1" s="34" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>345</v>
       </c>
@@ -15480,23 +15660,30 @@
         <v>174</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G2" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H2" s="29">
+      <c r="I2" s="29">
         <v>3</v>
       </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="9"/>
+      <c r="K2" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="30">
+      <c r="M2" s="42"/>
+      <c r="N2" s="36" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="30" hidden="1">
       <c r="A3" s="9" t="s">
         <v>475</v>
       </c>
@@ -15513,23 +15700,30 @@
         <v>174</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G3" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H3" s="38">
+      <c r="I3" s="35">
         <v>2</v>
       </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="9"/>
+      <c r="K3" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="20" customHeight="1">
+      <c r="M3" s="42"/>
+      <c r="N3" s="36" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>478</v>
       </c>
@@ -15546,23 +15740,30 @@
         <v>174</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G4" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H4" s="38">
+      <c r="I4" s="35">
         <v>1</v>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="9"/>
+      <c r="K4" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="L4" s="9" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="20" customHeight="1">
+      <c r="M4" s="42"/>
+      <c r="N4" s="36" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A5" s="9" t="s">
         <v>481</v>
       </c>
@@ -15579,23 +15780,30 @@
         <v>174</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G5" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H5" s="38">
+      <c r="I5" s="35">
         <v>2</v>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="9"/>
+      <c r="K5" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="L5" s="9" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="32" customHeight="1">
+      <c r="M5" s="42"/>
+      <c r="N5" s="36" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="32" hidden="1" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>349</v>
       </c>
@@ -15612,23 +15820,30 @@
         <v>174</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G6" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H6" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H6" s="29">
+      <c r="I6" s="29">
         <v>3</v>
       </c>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="9"/>
+      <c r="K6" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="L6" s="9" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="20" customHeight="1">
+      <c r="M6" s="42"/>
+      <c r="N6" s="36" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>484</v>
       </c>
@@ -15645,23 +15860,30 @@
         <v>174</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G7" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H7" s="38">
+      <c r="I7" s="35">
         <v>2</v>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="9"/>
+      <c r="K7" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="L7" s="9" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="20" customHeight="1">
+      <c r="M7" s="42"/>
+      <c r="N7" s="36" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>487</v>
       </c>
@@ -15678,23 +15900,30 @@
         <v>174</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G8" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H8" s="38">
+      <c r="I8" s="35">
         <v>1</v>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="9"/>
+      <c r="K8" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="L8" s="9" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="20" customHeight="1">
+      <c r="M8" s="42"/>
+      <c r="N8" s="36" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>490</v>
       </c>
@@ -15711,23 +15940,30 @@
         <v>174</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G9" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H9" s="38">
+      <c r="I9" s="35">
         <v>2</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="9"/>
+      <c r="K9" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="L9" s="9" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="20" customHeight="1">
+      <c r="M9" s="42"/>
+      <c r="N9" s="36" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>353</v>
       </c>
@@ -15744,23 +15980,30 @@
         <v>174</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G10" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H10" s="29">
+      <c r="I10" s="29">
         <v>5</v>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="9"/>
+      <c r="K10" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="L10" s="9" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="20" customHeight="1">
+      <c r="M10" s="42"/>
+      <c r="N10" s="37" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>493</v>
       </c>
@@ -15777,23 +16020,30 @@
         <v>174</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G11" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H11" s="38">
+      <c r="I11" s="35">
         <v>2</v>
       </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="9"/>
+      <c r="K11" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="L11" s="9" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="32" customHeight="1">
+      <c r="M11" s="42"/>
+      <c r="N11" s="37" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="32" hidden="1" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>496</v>
       </c>
@@ -15810,23 +16060,30 @@
         <v>174</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G12" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H12" s="38">
+      <c r="I12" s="35">
         <v>2</v>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="9"/>
+      <c r="K12" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="L12" s="9" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="20" customHeight="1">
+      <c r="M12" s="42"/>
+      <c r="N12" s="37" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A13" s="9" t="s">
         <v>499</v>
       </c>
@@ -15843,23 +16100,30 @@
         <v>174</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G13" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="H13" s="38">
+      <c r="I13" s="35">
         <v>1</v>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="9"/>
+      <c r="K13" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="L13" s="9" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="20" customHeight="1">
+      <c r="M13" s="42"/>
+      <c r="N13" s="37" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A14" s="9" t="s">
         <v>357</v>
       </c>
@@ -15876,23 +16140,30 @@
         <v>174</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G14" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H14" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="29">
+      <c r="I14" s="29">
         <v>2</v>
       </c>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="9"/>
+      <c r="K14" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="K14" s="9" t="s">
+      <c r="L14" s="9" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="20" customHeight="1">
+      <c r="M14" s="42"/>
+      <c r="N14" s="37" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>502</v>
       </c>
@@ -15909,23 +16180,30 @@
         <v>174</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G15" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H15" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H15" s="38">
+      <c r="I15" s="35">
         <v>1</v>
       </c>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="9"/>
+      <c r="K15" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="K15" s="9" t="s">
+      <c r="L15" s="9" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="33" customHeight="1">
+      <c r="M15" s="42"/>
+      <c r="N15" s="37" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="33" hidden="1" customHeight="1">
       <c r="A16" s="9" t="s">
         <v>505</v>
       </c>
@@ -15942,23 +16220,30 @@
         <v>174</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G16" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H16" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H16" s="38">
+      <c r="I16" s="35">
         <v>1</v>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="9"/>
+      <c r="K16" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="K16" s="9" t="s">
+      <c r="L16" s="9" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="20" customHeight="1">
+      <c r="M16" s="42"/>
+      <c r="N16" s="37" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A17" s="9" t="s">
         <v>508</v>
       </c>
@@ -15975,163 +16260,198 @@
         <v>174</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G17" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H17" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H17" s="38">
+      <c r="I17" s="35">
         <v>1</v>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="9"/>
+      <c r="K17" s="9" t="s">
         <v>510</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="L17" s="9" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M17" s="42"/>
+      <c r="N17" s="37" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>361</v>
+        <v>511</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>362</v>
+        <v>512</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>174</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G18" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H18" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H18" s="29">
+      <c r="I18" s="35">
         <v>3</v>
       </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9" t="s">
-        <v>363</v>
-      </c>
+      <c r="J18" s="9"/>
       <c r="K18" s="9" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="20" hidden="1" customHeight="1">
+        <v>513</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="M18" s="42"/>
+      <c r="N18" s="37" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>364</v>
+        <v>514</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>365</v>
+        <v>515</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>174</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G19" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H19" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H19" s="29">
-        <v>8</v>
-      </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9" t="s">
-        <v>366</v>
-      </c>
+      <c r="I19" s="35">
+        <v>5</v>
+      </c>
+      <c r="J19" s="9"/>
       <c r="K19" s="9" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="20" hidden="1" customHeight="1">
+        <v>516</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="M19" s="42"/>
+      <c r="N19" s="37" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>367</v>
+        <v>517</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>368</v>
+        <v>518</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>174</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G20" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H20" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H20" s="29">
-        <v>8</v>
-      </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9" t="s">
-        <v>369</v>
-      </c>
+      <c r="I20" s="35">
+        <v>5</v>
+      </c>
+      <c r="J20" s="9"/>
       <c r="K20" s="9" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="20" hidden="1" customHeight="1">
+        <v>519</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="M20" s="42"/>
+      <c r="N20" s="37" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>174</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G21" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H21" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H21" s="38">
+      <c r="I21" s="35">
         <v>3</v>
       </c>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9" t="s">
-        <v>513</v>
-      </c>
+      <c r="J21" s="9"/>
       <c r="K21" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="L21" s="9" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="32" hidden="1" customHeight="1">
+      <c r="M21" s="42"/>
+      <c r="N21" s="37" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="32" hidden="1" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>355</v>
@@ -16140,31 +16460,38 @@
         <v>174</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G22" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H22" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H22" s="38">
-        <v>5</v>
-      </c>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9" t="s">
-        <v>516</v>
-      </c>
+      <c r="I22" s="35">
+        <v>2</v>
+      </c>
+      <c r="J22" s="9"/>
       <c r="K22" s="9" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="34" hidden="1" customHeight="1">
+        <v>525</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="M22" s="42"/>
+      <c r="N22" s="37" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="34" hidden="1" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>355</v>
@@ -16173,163 +16500,202 @@
         <v>174</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G23" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H23" s="38">
-        <v>5</v>
-      </c>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9" t="s">
-        <v>519</v>
-      </c>
+      <c r="I23" s="35">
+        <v>2</v>
+      </c>
+      <c r="J23" s="9"/>
       <c r="K23" s="9" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="20" hidden="1" customHeight="1">
+        <v>528</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="M23" s="42"/>
+      <c r="N23" s="37" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>174</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G24" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H24" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H24" s="38">
+      <c r="I24" s="35">
         <v>3</v>
       </c>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9" t="s">
-        <v>522</v>
-      </c>
+      <c r="J24" s="9"/>
       <c r="K24" s="9" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="20" hidden="1" customHeight="1">
+        <v>531</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="M24" s="42"/>
+      <c r="N24" s="37" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="30" hidden="1" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>523</v>
+        <v>361</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>524</v>
+        <v>362</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>174</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G25" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H25" s="38">
-        <v>2</v>
-      </c>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9" t="s">
-        <v>525</v>
-      </c>
+      <c r="I25" s="29">
+        <v>3</v>
+      </c>
+      <c r="J25" s="9"/>
       <c r="K25" s="9" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="32" hidden="1" customHeight="1">
+        <v>363</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="M25" s="42" t="s">
+        <v>865</v>
+      </c>
+      <c r="N25" s="37" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="32" hidden="1" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>526</v>
+        <v>364</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>527</v>
+        <v>365</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>174</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G26" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H26" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H26" s="38">
-        <v>2</v>
-      </c>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9" t="s">
-        <v>528</v>
-      </c>
+      <c r="I26" s="29">
+        <v>8</v>
+      </c>
+      <c r="J26" s="9"/>
       <c r="K26" s="9" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="20" hidden="1" customHeight="1">
+        <v>366</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="M26" s="42" t="s">
+        <v>866</v>
+      </c>
+      <c r="N26" s="37" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A27" s="9" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>174</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G27" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H27" s="38">
-        <v>3</v>
-      </c>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9" t="s">
-        <v>531</v>
-      </c>
+      <c r="I27" s="35">
+        <v>2</v>
+      </c>
+      <c r="J27" s="9"/>
       <c r="K27" s="9" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="20" hidden="1" customHeight="1">
+        <v>534</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="M27" s="42"/>
+      <c r="N27" s="37" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A28" s="9" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>347</v>
@@ -16338,31 +16704,38 @@
         <v>174</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G28" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H28" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H28" s="38">
-        <v>2</v>
-      </c>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9" t="s">
-        <v>534</v>
-      </c>
+      <c r="I28" s="35">
+        <v>3</v>
+      </c>
+      <c r="J28" s="9"/>
       <c r="K28" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="L28" s="9" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M28" s="42"/>
+      <c r="N28" s="37" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A29" s="9" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>347</v>
@@ -16371,31 +16744,38 @@
         <v>174</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G29" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H29" s="38">
+      <c r="I29" s="35">
         <v>3</v>
       </c>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9" t="s">
-        <v>537</v>
-      </c>
+      <c r="J29" s="9"/>
       <c r="K29" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="L29" s="9" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M29" s="42"/>
+      <c r="N29" s="37" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>347</v>
@@ -16404,56 +16784,70 @@
         <v>174</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G30" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H30" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H30" s="38">
-        <v>3</v>
-      </c>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9" t="s">
-        <v>540</v>
-      </c>
+      <c r="I30" s="35">
+        <v>2</v>
+      </c>
+      <c r="J30" s="9"/>
       <c r="K30" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="L30" s="9" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M30" s="42"/>
+      <c r="N30" s="37" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A31" s="9" t="s">
-        <v>541</v>
+        <v>367</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>542</v>
+        <v>368</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>174</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H31" s="38">
-        <v>2</v>
-      </c>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9" t="s">
-        <v>543</v>
-      </c>
+      <c r="I31" s="29">
+        <v>8</v>
+      </c>
+      <c r="J31" s="9"/>
       <c r="K31" s="9" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="20" hidden="1" customHeight="1">
+        <v>369</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="M31" s="42"/>
+      <c r="N31" s="37" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>544</v>
       </c>
@@ -16470,23 +16864,30 @@
         <v>174</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G32" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H32" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H32" s="38">
+      <c r="I32" s="35">
         <v>3</v>
       </c>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9" t="s">
+      <c r="J32" s="9"/>
+      <c r="K32" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="K32" s="9" t="s">
+      <c r="L32" s="9" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M32" s="42"/>
+      <c r="N32" s="37" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A33" s="9" t="s">
         <v>547</v>
       </c>
@@ -16503,23 +16904,30 @@
         <v>174</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H33" s="38">
+      <c r="I33" s="35">
         <v>3</v>
       </c>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9" t="s">
+      <c r="J33" s="9"/>
+      <c r="K33" s="9" t="s">
         <v>549</v>
       </c>
-      <c r="K33" s="9" t="s">
+      <c r="L33" s="9" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M33" s="42"/>
+      <c r="N33" s="37" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>550</v>
       </c>
@@ -16536,23 +16944,30 @@
         <v>174</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G34" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H34" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H34" s="38">
+      <c r="I34" s="35">
         <v>3</v>
       </c>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9" t="s">
+      <c r="J34" s="9"/>
+      <c r="K34" s="9" t="s">
         <v>552</v>
       </c>
-      <c r="K34" s="9" t="s">
+      <c r="L34" s="9" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M34" s="42"/>
+      <c r="N34" s="37" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="20" hidden="1" customHeight="1">
       <c r="A35" s="9" t="s">
         <v>553</v>
       </c>
@@ -16569,34 +16984,41 @@
         <v>174</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H35" s="38">
+      <c r="I35" s="35">
         <v>2</v>
       </c>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9" t="s">
+      <c r="J35" s="9"/>
+      <c r="K35" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="K35" s="9" t="s">
+      <c r="L35" s="9" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M35" s="42"/>
+      <c r="N35" s="37" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="20" customHeight="1">
       <c r="A36" s="9" t="s">
-        <v>370</v>
+        <v>556</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>207</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>371</v>
+        <v>557</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>174</v>
@@ -16604,32 +17026,34 @@
       <c r="F36" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="9"/>
+      <c r="H36" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H36" s="29">
-        <v>8</v>
-      </c>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9" t="s">
-        <v>372</v>
-      </c>
+      <c r="I36" s="35">
+        <v>3</v>
+      </c>
+      <c r="J36" s="9"/>
       <c r="K36" s="9" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="20" hidden="1" customHeight="1">
+        <v>558</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M36" s="42"/>
+    </row>
+    <row r="37" spans="1:14" ht="20" customHeight="1">
       <c r="A37" s="9" t="s">
-        <v>373</v>
+        <v>559</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>207</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>374</v>
+        <v>560</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>174</v>
@@ -16637,32 +17061,34 @@
       <c r="F37" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G37" s="9" t="s">
+      <c r="G37" s="9"/>
+      <c r="H37" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H37" s="29">
+      <c r="I37" s="35">
         <v>5</v>
       </c>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9" t="s">
-        <v>375</v>
-      </c>
+      <c r="J37" s="9"/>
       <c r="K37" s="9" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="33" hidden="1" customHeight="1">
+        <v>561</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="M37" s="42"/>
+    </row>
+    <row r="38" spans="1:14" ht="33" customHeight="1">
       <c r="A38" s="9" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>207</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>174</v>
@@ -16670,29 +17096,31 @@
       <c r="F38" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G38" s="9" t="s">
+      <c r="G38" s="9"/>
+      <c r="H38" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H38" s="38">
+      <c r="I38" s="35">
         <v>3</v>
       </c>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9" t="s">
-        <v>558</v>
-      </c>
+      <c r="J38" s="9"/>
       <c r="K38" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="L38" s="9" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M38" s="42"/>
+    </row>
+    <row r="39" spans="1:14" ht="20" customHeight="1">
       <c r="A39" s="9" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>207</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>347</v>
@@ -16703,29 +17131,31 @@
       <c r="F39" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="G39" s="9"/>
+      <c r="H39" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H39" s="38">
-        <v>5</v>
-      </c>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9" t="s">
-        <v>561</v>
-      </c>
+      <c r="I39" s="35">
+        <v>2</v>
+      </c>
+      <c r="J39" s="9"/>
       <c r="K39" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="L39" s="9" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M39" s="42"/>
+    </row>
+    <row r="40" spans="1:14" ht="20" customHeight="1">
       <c r="A40" s="9" t="s">
-        <v>562</v>
+        <v>370</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>207</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>563</v>
+        <v>371</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>347</v>
@@ -16736,32 +17166,34 @@
       <c r="F40" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="9"/>
+      <c r="H40" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H40" s="38">
-        <v>3</v>
-      </c>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9" t="s">
-        <v>564</v>
-      </c>
+      <c r="I40" s="29">
+        <v>8</v>
+      </c>
+      <c r="J40" s="9"/>
       <c r="K40" s="9" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="20" hidden="1" customHeight="1">
+        <v>372</v>
+      </c>
+      <c r="L40" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="M40" s="42"/>
+    </row>
+    <row r="41" spans="1:14" ht="20" customHeight="1">
       <c r="A41" s="9" t="s">
-        <v>565</v>
+        <v>373</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>207</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>566</v>
+        <v>374</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>174</v>
@@ -16769,21 +17201,23 @@
       <c r="F41" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="9"/>
+      <c r="H41" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H41" s="38">
-        <v>2</v>
-      </c>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9" t="s">
-        <v>567</v>
-      </c>
+      <c r="I41" s="29">
+        <v>5</v>
+      </c>
+      <c r="J41" s="9"/>
       <c r="K41" s="9" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="20" hidden="1" customHeight="1">
+        <v>375</v>
+      </c>
+      <c r="L41" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="M41" s="42"/>
+    </row>
+    <row r="42" spans="1:14" ht="20" customHeight="1">
       <c r="A42" s="9" t="s">
         <v>568</v>
       </c>
@@ -16802,21 +17236,23 @@
       <c r="F42" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G42" s="9" t="s">
+      <c r="G42" s="9"/>
+      <c r="H42" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H42" s="38">
+      <c r="I42" s="35">
         <v>3</v>
       </c>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9" t="s">
+      <c r="J42" s="9"/>
+      <c r="K42" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="K42" s="9" t="s">
+      <c r="L42" s="9" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M42" s="42"/>
+    </row>
+    <row r="43" spans="1:14" ht="20" customHeight="1">
       <c r="A43" s="9" t="s">
         <v>571</v>
       </c>
@@ -16835,21 +17271,23 @@
       <c r="F43" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G43" s="9" t="s">
+      <c r="G43" s="9"/>
+      <c r="H43" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H43" s="38">
+      <c r="I43" s="35">
         <v>5</v>
       </c>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9" t="s">
+      <c r="J43" s="9"/>
+      <c r="K43" s="9" t="s">
         <v>573</v>
       </c>
-      <c r="K43" s="9" t="s">
+      <c r="L43" s="9" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M43" s="42"/>
+    </row>
+    <row r="44" spans="1:14" ht="20" customHeight="1">
       <c r="A44" s="9" t="s">
         <v>574</v>
       </c>
@@ -16868,21 +17306,23 @@
       <c r="F44" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G44" s="9"/>
+      <c r="H44" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H44" s="38">
+      <c r="I44" s="35">
         <v>5</v>
       </c>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9" t="s">
+      <c r="J44" s="9"/>
+      <c r="K44" s="9" t="s">
         <v>576</v>
       </c>
-      <c r="K44" s="9" t="s">
+      <c r="L44" s="9" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M44" s="42"/>
+    </row>
+    <row r="45" spans="1:14" ht="20" customHeight="1">
       <c r="A45" s="9" t="s">
         <v>577</v>
       </c>
@@ -16901,21 +17341,23 @@
       <c r="F45" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G45" s="9" t="s">
+      <c r="G45" s="9"/>
+      <c r="H45" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H45" s="38">
+      <c r="I45" s="35">
         <v>5</v>
       </c>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9" t="s">
+      <c r="J45" s="9"/>
+      <c r="K45" s="9" t="s">
         <v>579</v>
       </c>
-      <c r="K45" s="9" t="s">
+      <c r="L45" s="9" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M45" s="42"/>
+    </row>
+    <row r="46" spans="1:14" ht="20" customHeight="1">
       <c r="A46" s="9" t="s">
         <v>580</v>
       </c>
@@ -16934,21 +17376,23 @@
       <c r="F46" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="9"/>
+      <c r="H46" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H46" s="38">
+      <c r="I46" s="35">
         <v>2</v>
       </c>
-      <c r="I46" s="9"/>
-      <c r="J46" s="9" t="s">
+      <c r="J46" s="9"/>
+      <c r="K46" s="9" t="s">
         <v>582</v>
       </c>
-      <c r="K46" s="9" t="s">
+      <c r="L46" s="9" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M46" s="42"/>
+    </row>
+    <row r="47" spans="1:14" ht="20" customHeight="1">
       <c r="A47" s="9" t="s">
         <v>583</v>
       </c>
@@ -16967,21 +17411,23 @@
       <c r="F47" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="G47" s="9"/>
+      <c r="H47" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H47" s="38">
+      <c r="I47" s="35">
         <v>3</v>
       </c>
-      <c r="I47" s="9"/>
-      <c r="J47" s="9" t="s">
+      <c r="J47" s="9"/>
+      <c r="K47" s="9" t="s">
         <v>585</v>
       </c>
-      <c r="K47" s="9" t="s">
+      <c r="L47" s="9" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M47" s="42"/>
+    </row>
+    <row r="48" spans="1:14" ht="20" customHeight="1">
       <c r="A48" s="9" t="s">
         <v>586</v>
       </c>
@@ -17000,21 +17446,23 @@
       <c r="F48" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G48" s="9" t="s">
+      <c r="G48" s="9"/>
+      <c r="H48" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H48" s="38">
+      <c r="I48" s="35">
         <v>3</v>
       </c>
-      <c r="I48" s="9"/>
-      <c r="J48" s="9" t="s">
+      <c r="J48" s="9"/>
+      <c r="K48" s="9" t="s">
         <v>588</v>
       </c>
-      <c r="K48" s="9" t="s">
+      <c r="L48" s="9" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M48" s="42"/>
+    </row>
+    <row r="49" spans="1:13" ht="20" customHeight="1">
       <c r="A49" s="9" t="s">
         <v>589</v>
       </c>
@@ -17033,21 +17481,23 @@
       <c r="F49" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G49" s="9" t="s">
+      <c r="G49" s="9"/>
+      <c r="H49" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H49" s="38">
+      <c r="I49" s="35">
         <v>5</v>
       </c>
-      <c r="I49" s="9"/>
-      <c r="J49" s="9" t="s">
+      <c r="J49" s="9"/>
+      <c r="K49" s="9" t="s">
         <v>591</v>
       </c>
-      <c r="K49" s="9" t="s">
+      <c r="L49" s="9" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M49" s="42"/>
+    </row>
+    <row r="50" spans="1:13" ht="20" customHeight="1">
       <c r="A50" s="9" t="s">
         <v>592</v>
       </c>
@@ -17066,21 +17516,23 @@
       <c r="F50" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="G50" s="9"/>
+      <c r="H50" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H50" s="38">
+      <c r="I50" s="35">
         <v>2</v>
       </c>
-      <c r="I50" s="9"/>
-      <c r="J50" s="9" t="s">
+      <c r="J50" s="9"/>
+      <c r="K50" s="9" t="s">
         <v>594</v>
       </c>
-      <c r="K50" s="9" t="s">
+      <c r="L50" s="9" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M50" s="42"/>
+    </row>
+    <row r="51" spans="1:13" ht="20" customHeight="1">
       <c r="A51" s="9" t="s">
         <v>595</v>
       </c>
@@ -17099,21 +17551,23 @@
       <c r="F51" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G51" s="9" t="s">
+      <c r="G51" s="9"/>
+      <c r="H51" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H51" s="38">
+      <c r="I51" s="35">
         <v>3</v>
       </c>
-      <c r="I51" s="9"/>
-      <c r="J51" s="9" t="s">
+      <c r="J51" s="9"/>
+      <c r="K51" s="9" t="s">
         <v>597</v>
       </c>
-      <c r="K51" s="9" t="s">
+      <c r="L51" s="9" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M51" s="42"/>
+    </row>
+    <row r="52" spans="1:13" ht="20" customHeight="1">
       <c r="A52" s="9" t="s">
         <v>598</v>
       </c>
@@ -17132,21 +17586,23 @@
       <c r="F52" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="G52" s="9"/>
+      <c r="H52" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H52" s="38">
+      <c r="I52" s="35">
         <v>3</v>
       </c>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9" t="s">
+      <c r="J52" s="9"/>
+      <c r="K52" s="9" t="s">
         <v>600</v>
       </c>
-      <c r="K52" s="9" t="s">
+      <c r="L52" s="9" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M52" s="42"/>
+    </row>
+    <row r="53" spans="1:13" ht="20" customHeight="1">
       <c r="A53" s="9" t="s">
         <v>601</v>
       </c>
@@ -17165,21 +17621,23 @@
       <c r="F53" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="G53" s="9"/>
+      <c r="H53" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H53" s="38">
+      <c r="I53" s="35">
         <v>2</v>
       </c>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9" t="s">
+      <c r="J53" s="9"/>
+      <c r="K53" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="K53" s="9" t="s">
+      <c r="L53" s="9" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M53" s="42"/>
+    </row>
+    <row r="54" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A54" s="9" t="s">
         <v>604</v>
       </c>
@@ -17198,21 +17656,23 @@
       <c r="F54" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G54" s="9" t="s">
+      <c r="G54" s="9"/>
+      <c r="H54" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H54" s="38">
+      <c r="I54" s="35">
         <v>5</v>
       </c>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9" t="s">
+      <c r="J54" s="9"/>
+      <c r="K54" s="9" t="s">
         <v>606</v>
       </c>
-      <c r="K54" s="9" t="s">
+      <c r="L54" s="9" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M54" s="42"/>
+    </row>
+    <row r="55" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A55" s="9" t="s">
         <v>607</v>
       </c>
@@ -17231,21 +17691,23 @@
       <c r="F55" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G55" s="9" t="s">
+      <c r="G55" s="9"/>
+      <c r="H55" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H55" s="38">
+      <c r="I55" s="35">
         <v>3</v>
       </c>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9" t="s">
+      <c r="J55" s="9"/>
+      <c r="K55" s="9" t="s">
         <v>609</v>
       </c>
-      <c r="K55" s="9" t="s">
+      <c r="L55" s="9" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M55" s="42"/>
+    </row>
+    <row r="56" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A56" s="9" t="s">
         <v>610</v>
       </c>
@@ -17264,21 +17726,23 @@
       <c r="F56" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G56" s="9" t="s">
+      <c r="G56" s="9"/>
+      <c r="H56" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H56" s="38">
+      <c r="I56" s="35">
         <v>3</v>
       </c>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9" t="s">
+      <c r="J56" s="9"/>
+      <c r="K56" s="9" t="s">
         <v>612</v>
       </c>
-      <c r="K56" s="9" t="s">
+      <c r="L56" s="9" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M56" s="42"/>
+    </row>
+    <row r="57" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A57" s="9" t="s">
         <v>613</v>
       </c>
@@ -17297,21 +17761,23 @@
       <c r="F57" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="G57" s="9"/>
+      <c r="H57" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H57" s="38">
+      <c r="I57" s="35">
         <v>5</v>
       </c>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9" t="s">
+      <c r="J57" s="9"/>
+      <c r="K57" s="9" t="s">
         <v>615</v>
       </c>
-      <c r="K57" s="9" t="s">
+      <c r="L57" s="9" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M57" s="42"/>
+    </row>
+    <row r="58" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A58" s="9" t="s">
         <v>616</v>
       </c>
@@ -17330,21 +17796,23 @@
       <c r="F58" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G58" s="9" t="s">
+      <c r="G58" s="9"/>
+      <c r="H58" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H58" s="38">
+      <c r="I58" s="35">
         <v>3</v>
       </c>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9" t="s">
+      <c r="J58" s="9"/>
+      <c r="K58" s="9" t="s">
         <v>618</v>
       </c>
-      <c r="K58" s="9" t="s">
+      <c r="L58" s="9" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M58" s="42"/>
+    </row>
+    <row r="59" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A59" s="9" t="s">
         <v>619</v>
       </c>
@@ -17363,21 +17831,23 @@
       <c r="F59" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G59" s="9" t="s">
+      <c r="G59" s="9"/>
+      <c r="H59" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H59" s="38">
+      <c r="I59" s="35">
         <v>3</v>
       </c>
-      <c r="I59" s="9"/>
-      <c r="J59" s="9" t="s">
+      <c r="J59" s="9"/>
+      <c r="K59" s="9" t="s">
         <v>621</v>
       </c>
-      <c r="K59" s="9" t="s">
+      <c r="L59" s="9" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M59" s="42"/>
+    </row>
+    <row r="60" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A60" s="9" t="s">
         <v>622</v>
       </c>
@@ -17396,21 +17866,23 @@
       <c r="F60" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G60" s="9" t="s">
+      <c r="G60" s="9"/>
+      <c r="H60" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H60" s="38">
+      <c r="I60" s="35">
         <v>5</v>
       </c>
-      <c r="I60" s="9"/>
-      <c r="J60" s="9" t="s">
+      <c r="J60" s="9"/>
+      <c r="K60" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="K60" s="9" t="s">
+      <c r="L60" s="9" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M60" s="42"/>
+    </row>
+    <row r="61" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A61" s="9" t="s">
         <v>625</v>
       </c>
@@ -17429,21 +17901,23 @@
       <c r="F61" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G61" s="9" t="s">
+      <c r="G61" s="9"/>
+      <c r="H61" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H61" s="38">
+      <c r="I61" s="35">
         <v>5</v>
       </c>
-      <c r="I61" s="9"/>
-      <c r="J61" s="9" t="s">
+      <c r="J61" s="9"/>
+      <c r="K61" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="K61" s="9" t="s">
+      <c r="L61" s="9" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M61" s="42"/>
+    </row>
+    <row r="62" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A62" s="9" t="s">
         <v>627</v>
       </c>
@@ -17462,21 +17936,23 @@
       <c r="F62" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G62" s="9" t="s">
+      <c r="G62" s="9"/>
+      <c r="H62" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H62" s="38">
+      <c r="I62" s="35">
         <v>5</v>
       </c>
-      <c r="I62" s="9"/>
-      <c r="J62" s="9" t="s">
+      <c r="J62" s="9"/>
+      <c r="K62" s="9" t="s">
         <v>629</v>
       </c>
-      <c r="K62" s="9" t="s">
+      <c r="L62" s="9" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M62" s="42"/>
+    </row>
+    <row r="63" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A63" s="9" t="s">
         <v>630</v>
       </c>
@@ -17495,21 +17971,23 @@
       <c r="F63" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G63" s="9" t="s">
+      <c r="G63" s="9"/>
+      <c r="H63" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="H63" s="38">
+      <c r="I63" s="35">
         <v>3</v>
       </c>
-      <c r="I63" s="9"/>
-      <c r="J63" s="9" t="s">
+      <c r="J63" s="9"/>
+      <c r="K63" s="9" t="s">
         <v>632</v>
       </c>
-      <c r="K63" s="9" t="s">
+      <c r="L63" s="9" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" ht="33" hidden="1" customHeight="1">
+      <c r="M63" s="42"/>
+    </row>
+    <row r="64" spans="1:13" ht="33" hidden="1" customHeight="1">
       <c r="A64" s="9" t="s">
         <v>633</v>
       </c>
@@ -17528,21 +18006,23 @@
       <c r="F64" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G64" s="9" t="s">
+      <c r="G64" s="9"/>
+      <c r="H64" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H64" s="38">
+      <c r="I64" s="35">
         <v>2</v>
       </c>
-      <c r="I64" s="9"/>
-      <c r="J64" s="9" t="s">
+      <c r="J64" s="9"/>
+      <c r="K64" s="9" t="s">
         <v>635</v>
       </c>
-      <c r="K64" s="9" t="s">
+      <c r="L64" s="9" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M64" s="42"/>
+    </row>
+    <row r="65" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A65" s="9" t="s">
         <v>636</v>
       </c>
@@ -17561,21 +18041,23 @@
       <c r="F65" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G65" s="9" t="s">
+      <c r="G65" s="9"/>
+      <c r="H65" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H65" s="38">
+      <c r="I65" s="35">
         <v>2</v>
       </c>
-      <c r="I65" s="9"/>
-      <c r="J65" s="9" t="s">
+      <c r="J65" s="9"/>
+      <c r="K65" s="9" t="s">
         <v>638</v>
       </c>
-      <c r="K65" s="9" t="s">
+      <c r="L65" s="9" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M65" s="42"/>
+    </row>
+    <row r="66" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A66" s="9" t="s">
         <v>639</v>
       </c>
@@ -17594,21 +18076,23 @@
       <c r="F66" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G66" s="9" t="s">
+      <c r="G66" s="9"/>
+      <c r="H66" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H66" s="38">
+      <c r="I66" s="35">
         <v>3</v>
       </c>
-      <c r="I66" s="9"/>
-      <c r="J66" s="9" t="s">
+      <c r="J66" s="9"/>
+      <c r="K66" s="9" t="s">
         <v>641</v>
       </c>
-      <c r="K66" s="9" t="s">
+      <c r="L66" s="9" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M66" s="42"/>
+    </row>
+    <row r="67" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A67" s="9" t="s">
         <v>642</v>
       </c>
@@ -17627,21 +18111,23 @@
       <c r="F67" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G67" s="9" t="s">
+      <c r="G67" s="9"/>
+      <c r="H67" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H67" s="38">
+      <c r="I67" s="35">
         <v>5</v>
       </c>
-      <c r="I67" s="9"/>
-      <c r="J67" s="9" t="s">
+      <c r="J67" s="9"/>
+      <c r="K67" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="K67" s="9" t="s">
+      <c r="L67" s="9" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M67" s="42"/>
+    </row>
+    <row r="68" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A68" s="9" t="s">
         <v>645</v>
       </c>
@@ -17660,21 +18146,23 @@
       <c r="F68" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G68" s="9" t="s">
+      <c r="G68" s="9"/>
+      <c r="H68" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H68" s="38">
+      <c r="I68" s="35">
         <v>5</v>
       </c>
-      <c r="I68" s="9"/>
-      <c r="J68" s="9" t="s">
+      <c r="J68" s="9"/>
+      <c r="K68" s="9" t="s">
         <v>647</v>
       </c>
-      <c r="K68" s="9" t="s">
+      <c r="L68" s="9" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M68" s="42"/>
+    </row>
+    <row r="69" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A69" s="9" t="s">
         <v>648</v>
       </c>
@@ -17693,21 +18181,23 @@
       <c r="F69" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G69" s="9" t="s">
+      <c r="G69" s="9"/>
+      <c r="H69" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H69" s="38">
+      <c r="I69" s="35">
         <v>5</v>
       </c>
-      <c r="I69" s="9"/>
-      <c r="J69" s="9" t="s">
+      <c r="J69" s="9"/>
+      <c r="K69" s="9" t="s">
         <v>650</v>
       </c>
-      <c r="K69" s="9" t="s">
+      <c r="L69" s="9" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M69" s="42"/>
+    </row>
+    <row r="70" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A70" s="9" t="s">
         <v>651</v>
       </c>
@@ -17726,21 +18216,23 @@
       <c r="F70" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G70" s="9" t="s">
+      <c r="G70" s="9"/>
+      <c r="H70" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H70" s="38">
+      <c r="I70" s="35">
         <v>3</v>
       </c>
-      <c r="I70" s="9"/>
-      <c r="J70" s="9" t="s">
+      <c r="J70" s="9"/>
+      <c r="K70" s="9" t="s">
         <v>653</v>
       </c>
-      <c r="K70" s="9" t="s">
+      <c r="L70" s="9" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M70" s="42"/>
+    </row>
+    <row r="71" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A71" s="9" t="s">
         <v>376</v>
       </c>
@@ -17759,21 +18251,23 @@
       <c r="F71" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G71" s="9" t="s">
+      <c r="G71" s="9"/>
+      <c r="H71" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="H71" s="29">
+      <c r="I71" s="29">
         <v>5</v>
       </c>
-      <c r="I71" s="9"/>
-      <c r="J71" s="9" t="s">
+      <c r="J71" s="9"/>
+      <c r="K71" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="K71" s="9" t="s">
+      <c r="L71" s="9" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M71" s="42"/>
+    </row>
+    <row r="72" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A72" s="9" t="s">
         <v>654</v>
       </c>
@@ -17792,21 +18286,23 @@
       <c r="F72" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G72" s="9" t="s">
+      <c r="G72" s="9"/>
+      <c r="H72" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H72" s="38">
+      <c r="I72" s="35">
         <v>5</v>
       </c>
-      <c r="I72" s="9"/>
-      <c r="J72" s="9" t="s">
+      <c r="J72" s="9"/>
+      <c r="K72" s="9" t="s">
         <v>656</v>
       </c>
-      <c r="K72" s="9" t="s">
+      <c r="L72" s="9" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M72" s="42"/>
+    </row>
+    <row r="73" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A73" s="9" t="s">
         <v>657</v>
       </c>
@@ -17825,21 +18321,23 @@
       <c r="F73" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G73" s="9" t="s">
+      <c r="G73" s="9"/>
+      <c r="H73" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H73" s="38">
+      <c r="I73" s="35">
         <v>2</v>
       </c>
-      <c r="I73" s="9"/>
-      <c r="J73" s="9" t="s">
+      <c r="J73" s="9"/>
+      <c r="K73" s="9" t="s">
         <v>659</v>
       </c>
-      <c r="K73" s="9" t="s">
+      <c r="L73" s="9" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" ht="32" hidden="1" customHeight="1">
+      <c r="M73" s="42"/>
+    </row>
+    <row r="74" spans="1:13" ht="32" hidden="1" customHeight="1">
       <c r="A74" s="9" t="s">
         <v>660</v>
       </c>
@@ -17858,21 +18356,23 @@
       <c r="F74" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G74" s="9" t="s">
+      <c r="G74" s="9"/>
+      <c r="H74" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="H74" s="38">
+      <c r="I74" s="35">
         <v>3</v>
       </c>
-      <c r="I74" s="9"/>
-      <c r="J74" s="9" t="s">
+      <c r="J74" s="9"/>
+      <c r="K74" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="K74" s="9" t="s">
+      <c r="L74" s="9" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M74" s="42"/>
+    </row>
+    <row r="75" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A75" s="9" t="s">
         <v>663</v>
       </c>
@@ -17891,21 +18391,23 @@
       <c r="F75" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G75" s="9" t="s">
+      <c r="G75" s="9"/>
+      <c r="H75" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H75" s="38">
+      <c r="I75" s="35">
         <v>5</v>
       </c>
-      <c r="I75" s="9"/>
-      <c r="J75" s="9" t="s">
+      <c r="J75" s="9"/>
+      <c r="K75" s="9" t="s">
         <v>665</v>
       </c>
-      <c r="K75" s="9" t="s">
+      <c r="L75" s="9" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M75" s="42"/>
+    </row>
+    <row r="76" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A76" s="9" t="s">
         <v>666</v>
       </c>
@@ -17924,21 +18426,23 @@
       <c r="F76" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G76" s="9" t="s">
+      <c r="G76" s="9"/>
+      <c r="H76" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H76" s="38">
+      <c r="I76" s="35">
         <v>5</v>
       </c>
-      <c r="I76" s="9"/>
-      <c r="J76" s="9" t="s">
+      <c r="J76" s="9"/>
+      <c r="K76" s="9" t="s">
         <v>668</v>
       </c>
-      <c r="K76" s="9" t="s">
+      <c r="L76" s="9" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M76" s="42"/>
+    </row>
+    <row r="77" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A77" s="9" t="s">
         <v>669</v>
       </c>
@@ -17957,21 +18461,23 @@
       <c r="F77" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G77" s="9" t="s">
+      <c r="G77" s="9"/>
+      <c r="H77" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H77" s="38">
+      <c r="I77" s="35">
         <v>3</v>
       </c>
-      <c r="I77" s="9"/>
-      <c r="J77" s="9" t="s">
+      <c r="J77" s="9"/>
+      <c r="K77" s="9" t="s">
         <v>671</v>
       </c>
-      <c r="K77" s="9" t="s">
+      <c r="L77" s="9" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" ht="32" hidden="1" customHeight="1">
+      <c r="M77" s="42"/>
+    </row>
+    <row r="78" spans="1:13" ht="32" hidden="1" customHeight="1">
       <c r="A78" s="9" t="s">
         <v>672</v>
       </c>
@@ -17990,21 +18496,23 @@
       <c r="F78" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G78" s="9" t="s">
+      <c r="G78" s="9"/>
+      <c r="H78" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H78" s="38">
+      <c r="I78" s="35">
         <v>5</v>
       </c>
-      <c r="I78" s="9"/>
-      <c r="J78" s="9" t="s">
+      <c r="J78" s="9"/>
+      <c r="K78" s="9" t="s">
         <v>674</v>
       </c>
-      <c r="K78" s="9" t="s">
+      <c r="L78" s="9" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M78" s="42"/>
+    </row>
+    <row r="79" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A79" s="9" t="s">
         <v>675</v>
       </c>
@@ -18023,21 +18531,23 @@
       <c r="F79" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G79" s="9" t="s">
+      <c r="G79" s="9"/>
+      <c r="H79" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H79" s="38">
+      <c r="I79" s="35">
         <v>3</v>
       </c>
-      <c r="I79" s="9"/>
-      <c r="J79" s="9" t="s">
+      <c r="J79" s="9"/>
+      <c r="K79" s="9" t="s">
         <v>677</v>
       </c>
-      <c r="K79" s="9" t="s">
+      <c r="L79" s="9" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M79" s="42"/>
+    </row>
+    <row r="80" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A80" s="9" t="s">
         <v>678</v>
       </c>
@@ -18056,21 +18566,23 @@
       <c r="F80" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G80" s="9" t="s">
+      <c r="G80" s="9"/>
+      <c r="H80" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H80" s="38">
+      <c r="I80" s="35">
         <v>3</v>
       </c>
-      <c r="I80" s="9"/>
-      <c r="J80" s="9" t="s">
+      <c r="J80" s="9"/>
+      <c r="K80" s="9" t="s">
         <v>680</v>
       </c>
-      <c r="K80" s="9" t="s">
+      <c r="L80" s="9" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" ht="32" hidden="1" customHeight="1">
+      <c r="M80" s="42"/>
+    </row>
+    <row r="81" spans="1:13" ht="32" hidden="1" customHeight="1">
       <c r="A81" s="9" t="s">
         <v>681</v>
       </c>
@@ -18089,21 +18601,23 @@
       <c r="F81" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G81" s="9" t="s">
+      <c r="G81" s="9"/>
+      <c r="H81" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H81" s="38">
+      <c r="I81" s="35">
         <v>3</v>
       </c>
-      <c r="I81" s="9"/>
-      <c r="J81" s="9" t="s">
+      <c r="J81" s="9"/>
+      <c r="K81" s="9" t="s">
         <v>683</v>
       </c>
-      <c r="K81" s="9" t="s">
+      <c r="L81" s="9" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M81" s="42"/>
+    </row>
+    <row r="82" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A82" s="9" t="s">
         <v>684</v>
       </c>
@@ -18122,21 +18636,23 @@
       <c r="F82" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G82" s="9" t="s">
+      <c r="G82" s="9"/>
+      <c r="H82" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H82" s="38">
+      <c r="I82" s="35">
         <v>3</v>
       </c>
-      <c r="I82" s="9"/>
-      <c r="J82" s="9" t="s">
+      <c r="J82" s="9"/>
+      <c r="K82" s="9" t="s">
         <v>686</v>
       </c>
-      <c r="K82" s="9" t="s">
+      <c r="L82" s="9" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" ht="32" hidden="1" customHeight="1">
+      <c r="M82" s="42"/>
+    </row>
+    <row r="83" spans="1:13" ht="32" hidden="1" customHeight="1">
       <c r="A83" s="9" t="s">
         <v>687</v>
       </c>
@@ -18155,21 +18671,23 @@
       <c r="F83" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G83" s="9" t="s">
+      <c r="G83" s="9"/>
+      <c r="H83" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H83" s="38">
+      <c r="I83" s="35">
         <v>5</v>
       </c>
-      <c r="I83" s="9"/>
-      <c r="J83" s="9" t="s">
+      <c r="J83" s="9"/>
+      <c r="K83" s="9" t="s">
         <v>689</v>
       </c>
-      <c r="K83" s="9" t="s">
+      <c r="L83" s="9" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M83" s="42"/>
+    </row>
+    <row r="84" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A84" s="9" t="s">
         <v>690</v>
       </c>
@@ -18188,21 +18706,23 @@
       <c r="F84" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G84" s="9" t="s">
+      <c r="G84" s="9"/>
+      <c r="H84" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H84" s="38">
+      <c r="I84" s="35">
         <v>3</v>
       </c>
-      <c r="I84" s="9"/>
-      <c r="J84" s="9" t="s">
+      <c r="J84" s="9"/>
+      <c r="K84" s="9" t="s">
         <v>692</v>
       </c>
-      <c r="K84" s="9" t="s">
+      <c r="L84" s="9" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M84" s="42"/>
+    </row>
+    <row r="85" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A85" s="9" t="s">
         <v>693</v>
       </c>
@@ -18221,21 +18741,23 @@
       <c r="F85" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G85" s="9" t="s">
+      <c r="G85" s="9"/>
+      <c r="H85" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H85" s="38">
+      <c r="I85" s="35">
         <v>5</v>
       </c>
-      <c r="I85" s="9"/>
-      <c r="J85" s="9" t="s">
+      <c r="J85" s="9"/>
+      <c r="K85" s="9" t="s">
         <v>695</v>
       </c>
-      <c r="K85" s="9" t="s">
+      <c r="L85" s="9" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M85" s="42"/>
+    </row>
+    <row r="86" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A86" s="9" t="s">
         <v>696</v>
       </c>
@@ -18254,21 +18776,23 @@
       <c r="F86" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G86" s="9" t="s">
+      <c r="G86" s="9"/>
+      <c r="H86" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H86" s="38">
+      <c r="I86" s="35">
         <v>5</v>
       </c>
-      <c r="I86" s="9"/>
-      <c r="J86" s="9" t="s">
+      <c r="J86" s="9"/>
+      <c r="K86" s="9" t="s">
         <v>698</v>
       </c>
-      <c r="K86" s="9" t="s">
+      <c r="L86" s="9" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M86" s="42"/>
+    </row>
+    <row r="87" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A87" s="9" t="s">
         <v>699</v>
       </c>
@@ -18287,21 +18811,23 @@
       <c r="F87" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G87" s="9" t="s">
+      <c r="G87" s="9"/>
+      <c r="H87" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H87" s="38">
+      <c r="I87" s="35">
         <v>5</v>
       </c>
-      <c r="I87" s="9"/>
-      <c r="J87" s="9" t="s">
+      <c r="J87" s="9"/>
+      <c r="K87" s="9" t="s">
         <v>701</v>
       </c>
-      <c r="K87" s="9" t="s">
+      <c r="L87" s="9" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M87" s="42"/>
+    </row>
+    <row r="88" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A88" s="9" t="s">
         <v>702</v>
       </c>
@@ -18320,21 +18846,23 @@
       <c r="F88" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G88" s="9" t="s">
+      <c r="G88" s="9"/>
+      <c r="H88" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H88" s="38">
+      <c r="I88" s="35">
         <v>5</v>
       </c>
-      <c r="I88" s="9"/>
-      <c r="J88" s="9" t="s">
+      <c r="J88" s="9"/>
+      <c r="K88" s="9" t="s">
         <v>704</v>
       </c>
-      <c r="K88" s="9" t="s">
+      <c r="L88" s="9" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M88" s="42"/>
+    </row>
+    <row r="89" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A89" s="9" t="s">
         <v>705</v>
       </c>
@@ -18353,21 +18881,23 @@
       <c r="F89" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G89" s="9" t="s">
+      <c r="G89" s="9"/>
+      <c r="H89" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H89" s="38">
+      <c r="I89" s="35">
         <v>3</v>
       </c>
-      <c r="I89" s="9"/>
-      <c r="J89" s="9" t="s">
+      <c r="J89" s="9"/>
+      <c r="K89" s="9" t="s">
         <v>707</v>
       </c>
-      <c r="K89" s="9" t="s">
+      <c r="L89" s="9" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M89" s="42"/>
+    </row>
+    <row r="90" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A90" s="9" t="s">
         <v>708</v>
       </c>
@@ -18386,21 +18916,23 @@
       <c r="F90" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G90" s="9" t="s">
+      <c r="G90" s="9"/>
+      <c r="H90" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H90" s="38">
+      <c r="I90" s="35">
         <v>5</v>
       </c>
-      <c r="I90" s="9"/>
-      <c r="J90" s="9" t="s">
+      <c r="J90" s="9"/>
+      <c r="K90" s="9" t="s">
         <v>710</v>
       </c>
-      <c r="K90" s="9" t="s">
+      <c r="L90" s="9" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" ht="32" hidden="1" customHeight="1">
+      <c r="M90" s="42"/>
+    </row>
+    <row r="91" spans="1:13" ht="32" hidden="1" customHeight="1">
       <c r="A91" s="9" t="s">
         <v>711</v>
       </c>
@@ -18419,21 +18951,23 @@
       <c r="F91" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G91" s="9" t="s">
+      <c r="G91" s="9"/>
+      <c r="H91" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H91" s="38">
+      <c r="I91" s="35">
         <v>3</v>
       </c>
-      <c r="I91" s="9"/>
-      <c r="J91" s="9" t="s">
+      <c r="J91" s="9"/>
+      <c r="K91" s="9" t="s">
         <v>713</v>
       </c>
-      <c r="K91" s="9" t="s">
+      <c r="L91" s="9" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M91" s="42"/>
+    </row>
+    <row r="92" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A92" s="9" t="s">
         <v>714</v>
       </c>
@@ -18452,21 +18986,23 @@
       <c r="F92" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G92" s="9" t="s">
+      <c r="G92" s="9"/>
+      <c r="H92" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H92" s="38">
+      <c r="I92" s="35">
         <v>5</v>
       </c>
-      <c r="I92" s="9"/>
-      <c r="J92" s="9" t="s">
+      <c r="J92" s="9"/>
+      <c r="K92" s="9" t="s">
         <v>716</v>
       </c>
-      <c r="K92" s="9" t="s">
+      <c r="L92" s="9" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M92" s="42"/>
+    </row>
+    <row r="93" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A93" s="9" t="s">
         <v>717</v>
       </c>
@@ -18485,21 +19021,23 @@
       <c r="F93" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G93" s="9" t="s">
+      <c r="G93" s="9"/>
+      <c r="H93" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H93" s="38">
+      <c r="I93" s="35">
         <v>5</v>
       </c>
-      <c r="I93" s="9"/>
-      <c r="J93" s="9" t="s">
+      <c r="J93" s="9"/>
+      <c r="K93" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="K93" s="9" t="s">
+      <c r="L93" s="9" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M93" s="42"/>
+    </row>
+    <row r="94" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A94" s="9" t="s">
         <v>720</v>
       </c>
@@ -18518,21 +19056,23 @@
       <c r="F94" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G94" s="9" t="s">
+      <c r="G94" s="9"/>
+      <c r="H94" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H94" s="38">
+      <c r="I94" s="35">
         <v>3</v>
       </c>
-      <c r="I94" s="9"/>
-      <c r="J94" s="9" t="s">
+      <c r="J94" s="9"/>
+      <c r="K94" s="9" t="s">
         <v>722</v>
       </c>
-      <c r="K94" s="9" t="s">
+      <c r="L94" s="9" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M94" s="42"/>
+    </row>
+    <row r="95" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A95" s="9" t="s">
         <v>723</v>
       </c>
@@ -18551,21 +19091,23 @@
       <c r="F95" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G95" s="9" t="s">
+      <c r="G95" s="9"/>
+      <c r="H95" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="H95" s="38">
+      <c r="I95" s="35">
         <v>3</v>
       </c>
-      <c r="I95" s="9"/>
-      <c r="J95" s="9" t="s">
+      <c r="J95" s="9"/>
+      <c r="K95" s="9" t="s">
         <v>725</v>
       </c>
-      <c r="K95" s="9" t="s">
+      <c r="L95" s="9" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="96" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M95" s="42"/>
+    </row>
+    <row r="96" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A96" s="9" t="s">
         <v>726</v>
       </c>
@@ -18584,21 +19126,23 @@
       <c r="F96" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G96" s="9" t="s">
+      <c r="G96" s="9"/>
+      <c r="H96" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H96" s="38">
+      <c r="I96" s="35">
         <v>3</v>
       </c>
-      <c r="I96" s="9"/>
-      <c r="J96" s="9" t="s">
+      <c r="J96" s="9"/>
+      <c r="K96" s="9" t="s">
         <v>728</v>
       </c>
-      <c r="K96" s="9" t="s">
+      <c r="L96" s="9" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="97" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M96" s="42"/>
+    </row>
+    <row r="97" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A97" s="9" t="s">
         <v>729</v>
       </c>
@@ -18617,21 +19161,23 @@
       <c r="F97" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G97" s="9" t="s">
+      <c r="G97" s="9"/>
+      <c r="H97" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H97" s="38">
+      <c r="I97" s="35">
         <v>2</v>
       </c>
-      <c r="I97" s="9"/>
-      <c r="J97" s="9" t="s">
+      <c r="J97" s="9"/>
+      <c r="K97" s="9" t="s">
         <v>731</v>
       </c>
-      <c r="K97" s="9" t="s">
+      <c r="L97" s="9" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="98" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M97" s="42"/>
+    </row>
+    <row r="98" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A98" s="9" t="s">
         <v>732</v>
       </c>
@@ -18650,21 +19196,23 @@
       <c r="F98" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G98" s="9" t="s">
+      <c r="G98" s="9"/>
+      <c r="H98" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H98" s="38">
+      <c r="I98" s="35">
         <v>3</v>
       </c>
-      <c r="I98" s="9"/>
-      <c r="J98" s="9" t="s">
+      <c r="J98" s="9"/>
+      <c r="K98" s="9" t="s">
         <v>734</v>
       </c>
-      <c r="K98" s="9" t="s">
+      <c r="L98" s="9" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="99" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M98" s="42"/>
+    </row>
+    <row r="99" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A99" s="9" t="s">
         <v>735</v>
       </c>
@@ -18683,21 +19231,23 @@
       <c r="F99" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G99" s="9" t="s">
+      <c r="G99" s="9"/>
+      <c r="H99" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H99" s="38">
+      <c r="I99" s="35">
         <v>2</v>
       </c>
-      <c r="I99" s="9"/>
-      <c r="J99" s="9" t="s">
+      <c r="J99" s="9"/>
+      <c r="K99" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="K99" s="9" t="s">
+      <c r="L99" s="9" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="100" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M99" s="42"/>
+    </row>
+    <row r="100" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A100" s="9" t="s">
         <v>738</v>
       </c>
@@ -18716,21 +19266,23 @@
       <c r="F100" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G100" s="9" t="s">
+      <c r="G100" s="9"/>
+      <c r="H100" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H100" s="38">
+      <c r="I100" s="35">
         <v>3</v>
       </c>
-      <c r="I100" s="9"/>
-      <c r="J100" s="9" t="s">
+      <c r="J100" s="9"/>
+      <c r="K100" s="9" t="s">
         <v>740</v>
       </c>
-      <c r="K100" s="9" t="s">
+      <c r="L100" s="9" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="101" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M100" s="42"/>
+    </row>
+    <row r="101" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A101" s="9" t="s">
         <v>741</v>
       </c>
@@ -18749,21 +19301,23 @@
       <c r="F101" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G101" s="9" t="s">
+      <c r="G101" s="9"/>
+      <c r="H101" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H101" s="38">
+      <c r="I101" s="35">
         <v>3</v>
       </c>
-      <c r="I101" s="9"/>
-      <c r="J101" s="9" t="s">
+      <c r="J101" s="9"/>
+      <c r="K101" s="9" t="s">
         <v>743</v>
       </c>
-      <c r="K101" s="9" t="s">
+      <c r="L101" s="9" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="102" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M101" s="42"/>
+    </row>
+    <row r="102" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A102" s="9" t="s">
         <v>744</v>
       </c>
@@ -18782,21 +19336,23 @@
       <c r="F102" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G102" s="9" t="s">
+      <c r="G102" s="9"/>
+      <c r="H102" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H102" s="38">
+      <c r="I102" s="35">
         <v>5</v>
       </c>
-      <c r="I102" s="9"/>
-      <c r="J102" s="9" t="s">
+      <c r="J102" s="9"/>
+      <c r="K102" s="9" t="s">
         <v>746</v>
       </c>
-      <c r="K102" s="9" t="s">
+      <c r="L102" s="9" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="103" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M102" s="42"/>
+    </row>
+    <row r="103" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A103" s="9" t="s">
         <v>747</v>
       </c>
@@ -18815,21 +19371,23 @@
       <c r="F103" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G103" s="9" t="s">
+      <c r="G103" s="9"/>
+      <c r="H103" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H103" s="38">
+      <c r="I103" s="35">
         <v>5</v>
       </c>
-      <c r="I103" s="9"/>
-      <c r="J103" s="9" t="s">
+      <c r="J103" s="9"/>
+      <c r="K103" s="9" t="s">
         <v>749</v>
       </c>
-      <c r="K103" s="9" t="s">
+      <c r="L103" s="9" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="104" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M103" s="42"/>
+    </row>
+    <row r="104" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A104" s="9" t="s">
         <v>750</v>
       </c>
@@ -18848,21 +19406,23 @@
       <c r="F104" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G104" s="9" t="s">
+      <c r="G104" s="9"/>
+      <c r="H104" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H104" s="38">
+      <c r="I104" s="35">
         <v>3</v>
       </c>
-      <c r="I104" s="9"/>
-      <c r="J104" s="9" t="s">
+      <c r="J104" s="9"/>
+      <c r="K104" s="9" t="s">
         <v>752</v>
       </c>
-      <c r="K104" s="9" t="s">
+      <c r="L104" s="9" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="105" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M104" s="42"/>
+    </row>
+    <row r="105" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A105" s="9" t="s">
         <v>753</v>
       </c>
@@ -18881,21 +19441,23 @@
       <c r="F105" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G105" s="9" t="s">
+      <c r="G105" s="9"/>
+      <c r="H105" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H105" s="38">
+      <c r="I105" s="35">
         <v>3</v>
       </c>
-      <c r="I105" s="9"/>
-      <c r="J105" s="9" t="s">
+      <c r="J105" s="9"/>
+      <c r="K105" s="9" t="s">
         <v>755</v>
       </c>
-      <c r="K105" s="9" t="s">
+      <c r="L105" s="9" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="106" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M105" s="42"/>
+    </row>
+    <row r="106" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A106" s="9" t="s">
         <v>756</v>
       </c>
@@ -18914,21 +19476,23 @@
       <c r="F106" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G106" s="9" t="s">
+      <c r="G106" s="9"/>
+      <c r="H106" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H106" s="38">
+      <c r="I106" s="35">
         <v>3</v>
       </c>
-      <c r="I106" s="9"/>
-      <c r="J106" s="9" t="s">
+      <c r="J106" s="9"/>
+      <c r="K106" s="9" t="s">
         <v>758</v>
       </c>
-      <c r="K106" s="9" t="s">
+      <c r="L106" s="9" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="107" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M106" s="42"/>
+    </row>
+    <row r="107" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A107" s="9" t="s">
         <v>759</v>
       </c>
@@ -18947,21 +19511,23 @@
       <c r="F107" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G107" s="9" t="s">
+      <c r="G107" s="9"/>
+      <c r="H107" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H107" s="38">
+      <c r="I107" s="35">
         <v>3</v>
       </c>
-      <c r="I107" s="9"/>
-      <c r="J107" s="9" t="s">
+      <c r="J107" s="9"/>
+      <c r="K107" s="9" t="s">
         <v>761</v>
       </c>
-      <c r="K107" s="9" t="s">
+      <c r="L107" s="9" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="108" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M107" s="42"/>
+    </row>
+    <row r="108" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A108" s="9" t="s">
         <v>762</v>
       </c>
@@ -18980,21 +19546,23 @@
       <c r="F108" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G108" s="9" t="s">
+      <c r="G108" s="9"/>
+      <c r="H108" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H108" s="38">
+      <c r="I108" s="35">
         <v>5</v>
       </c>
-      <c r="I108" s="9"/>
-      <c r="J108" s="9" t="s">
+      <c r="J108" s="9"/>
+      <c r="K108" s="9" t="s">
         <v>764</v>
       </c>
-      <c r="K108" s="9" t="s">
+      <c r="L108" s="9" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="109" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M108" s="42"/>
+    </row>
+    <row r="109" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A109" s="9" t="s">
         <v>765</v>
       </c>
@@ -19013,21 +19581,23 @@
       <c r="F109" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G109" s="9" t="s">
+      <c r="G109" s="9"/>
+      <c r="H109" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H109" s="38">
+      <c r="I109" s="35">
         <v>5</v>
       </c>
-      <c r="I109" s="9"/>
-      <c r="J109" s="9" t="s">
+      <c r="J109" s="9"/>
+      <c r="K109" s="9" t="s">
         <v>767</v>
       </c>
-      <c r="K109" s="9" t="s">
+      <c r="L109" s="9" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="110" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M109" s="42"/>
+    </row>
+    <row r="110" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A110" s="9" t="s">
         <v>768</v>
       </c>
@@ -19046,21 +19616,23 @@
       <c r="F110" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G110" s="9" t="s">
+      <c r="G110" s="9"/>
+      <c r="H110" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H110" s="38">
+      <c r="I110" s="35">
         <v>2</v>
       </c>
-      <c r="I110" s="9"/>
-      <c r="J110" s="9" t="s">
+      <c r="J110" s="9"/>
+      <c r="K110" s="9" t="s">
         <v>770</v>
       </c>
-      <c r="K110" s="9" t="s">
+      <c r="L110" s="9" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="111" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M110" s="42"/>
+    </row>
+    <row r="111" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A111" s="9" t="s">
         <v>771</v>
       </c>
@@ -19079,21 +19651,23 @@
       <c r="F111" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G111" s="9" t="s">
+      <c r="G111" s="9"/>
+      <c r="H111" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H111" s="38">
+      <c r="I111" s="35">
         <v>5</v>
       </c>
-      <c r="I111" s="9"/>
-      <c r="J111" s="9" t="s">
+      <c r="J111" s="9"/>
+      <c r="K111" s="9" t="s">
         <v>773</v>
       </c>
-      <c r="K111" s="9" t="s">
+      <c r="L111" s="9" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="112" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M111" s="42"/>
+    </row>
+    <row r="112" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A112" s="9" t="s">
         <v>774</v>
       </c>
@@ -19112,21 +19686,23 @@
       <c r="F112" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G112" s="9" t="s">
+      <c r="G112" s="9"/>
+      <c r="H112" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H112" s="38">
+      <c r="I112" s="35">
         <v>3</v>
       </c>
-      <c r="I112" s="9"/>
-      <c r="J112" s="9" t="s">
+      <c r="J112" s="9"/>
+      <c r="K112" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="K112" s="9" t="s">
+      <c r="L112" s="9" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="113" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M112" s="42"/>
+    </row>
+    <row r="113" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A113" s="9" t="s">
         <v>777</v>
       </c>
@@ -19145,21 +19721,23 @@
       <c r="F113" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G113" s="9" t="s">
+      <c r="G113" s="9"/>
+      <c r="H113" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H113" s="38">
+      <c r="I113" s="35">
         <v>3</v>
       </c>
-      <c r="I113" s="9"/>
-      <c r="J113" s="9" t="s">
+      <c r="J113" s="9"/>
+      <c r="K113" s="9" t="s">
         <v>779</v>
       </c>
-      <c r="K113" s="9" t="s">
+      <c r="L113" s="9" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="114" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M113" s="42"/>
+    </row>
+    <row r="114" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A114" s="9" t="s">
         <v>780</v>
       </c>
@@ -19178,21 +19756,23 @@
       <c r="F114" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G114" s="9" t="s">
+      <c r="G114" s="9"/>
+      <c r="H114" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H114" s="38">
+      <c r="I114" s="35">
         <v>3</v>
       </c>
-      <c r="I114" s="9"/>
-      <c r="J114" s="9" t="s">
+      <c r="J114" s="9"/>
+      <c r="K114" s="9" t="s">
         <v>782</v>
       </c>
-      <c r="K114" s="9" t="s">
+      <c r="L114" s="9" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="115" spans="1:11" ht="32" hidden="1" customHeight="1">
+      <c r="M114" s="42"/>
+    </row>
+    <row r="115" spans="1:13" ht="32" hidden="1" customHeight="1">
       <c r="A115" s="9" t="s">
         <v>783</v>
       </c>
@@ -19211,21 +19791,23 @@
       <c r="F115" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G115" s="9" t="s">
+      <c r="G115" s="9"/>
+      <c r="H115" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H115" s="38">
+      <c r="I115" s="35">
         <v>3</v>
       </c>
-      <c r="I115" s="9"/>
-      <c r="J115" s="9" t="s">
+      <c r="J115" s="9"/>
+      <c r="K115" s="9" t="s">
         <v>785</v>
       </c>
-      <c r="K115" s="9" t="s">
+      <c r="L115" s="9" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="116" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M115" s="42"/>
+    </row>
+    <row r="116" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A116" s="9" t="s">
         <v>786</v>
       </c>
@@ -19244,21 +19826,23 @@
       <c r="F116" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G116" s="9" t="s">
+      <c r="G116" s="9"/>
+      <c r="H116" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H116" s="38">
+      <c r="I116" s="35">
         <v>2</v>
       </c>
-      <c r="I116" s="9"/>
-      <c r="J116" s="9" t="s">
+      <c r="J116" s="9"/>
+      <c r="K116" s="9" t="s">
         <v>788</v>
       </c>
-      <c r="K116" s="9" t="s">
+      <c r="L116" s="9" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="117" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M116" s="42"/>
+    </row>
+    <row r="117" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A117" s="9" t="s">
         <v>789</v>
       </c>
@@ -19277,21 +19861,23 @@
       <c r="F117" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G117" s="9" t="s">
+      <c r="G117" s="9"/>
+      <c r="H117" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H117" s="38">
+      <c r="I117" s="35">
         <v>3</v>
       </c>
-      <c r="I117" s="9"/>
-      <c r="J117" s="9" t="s">
+      <c r="J117" s="9"/>
+      <c r="K117" s="9" t="s">
         <v>791</v>
       </c>
-      <c r="K117" s="9" t="s">
+      <c r="L117" s="9" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="118" spans="1:11" ht="32" hidden="1" customHeight="1">
+      <c r="M117" s="42"/>
+    </row>
+    <row r="118" spans="1:13" ht="32" hidden="1" customHeight="1">
       <c r="A118" s="9" t="s">
         <v>792</v>
       </c>
@@ -19310,21 +19896,23 @@
       <c r="F118" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G118" s="9" t="s">
+      <c r="G118" s="9"/>
+      <c r="H118" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H118" s="38">
+      <c r="I118" s="35">
         <v>3</v>
       </c>
-      <c r="I118" s="9"/>
-      <c r="J118" s="9" t="s">
+      <c r="J118" s="9"/>
+      <c r="K118" s="9" t="s">
         <v>794</v>
       </c>
-      <c r="K118" s="9" t="s">
+      <c r="L118" s="9" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="119" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M118" s="42"/>
+    </row>
+    <row r="119" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A119" s="9" t="s">
         <v>795</v>
       </c>
@@ -19343,21 +19931,23 @@
       <c r="F119" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G119" s="9" t="s">
+      <c r="G119" s="9"/>
+      <c r="H119" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H119" s="38">
+      <c r="I119" s="35">
         <v>3</v>
       </c>
-      <c r="I119" s="9"/>
-      <c r="J119" s="9" t="s">
+      <c r="J119" s="9"/>
+      <c r="K119" s="9" t="s">
         <v>797</v>
       </c>
-      <c r="K119" s="9" t="s">
+      <c r="L119" s="9" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="120" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M119" s="42"/>
+    </row>
+    <row r="120" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A120" s="9" t="s">
         <v>798</v>
       </c>
@@ -19376,21 +19966,23 @@
       <c r="F120" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G120" s="9" t="s">
+      <c r="G120" s="9"/>
+      <c r="H120" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="H120" s="38">
+      <c r="I120" s="35">
         <v>3</v>
       </c>
-      <c r="I120" s="9"/>
-      <c r="J120" s="9" t="s">
+      <c r="J120" s="9"/>
+      <c r="K120" s="9" t="s">
         <v>800</v>
       </c>
-      <c r="K120" s="9" t="s">
+      <c r="L120" s="9" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="121" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M120" s="42"/>
+    </row>
+    <row r="121" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A121" s="9" t="s">
         <v>801</v>
       </c>
@@ -19409,21 +20001,23 @@
       <c r="F121" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G121" s="9" t="s">
+      <c r="G121" s="9"/>
+      <c r="H121" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="H121" s="38">
+      <c r="I121" s="35">
         <v>2</v>
       </c>
-      <c r="I121" s="9"/>
-      <c r="J121" s="9" t="s">
+      <c r="J121" s="9"/>
+      <c r="K121" s="9" t="s">
         <v>803</v>
       </c>
-      <c r="K121" s="9" t="s">
+      <c r="L121" s="9" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="122" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M121" s="42"/>
+    </row>
+    <row r="122" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A122" s="9" t="s">
         <v>804</v>
       </c>
@@ -19442,21 +20036,23 @@
       <c r="F122" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G122" s="9" t="s">
+      <c r="G122" s="9"/>
+      <c r="H122" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="H122" s="38">
+      <c r="I122" s="35">
         <v>3</v>
       </c>
-      <c r="I122" s="9"/>
-      <c r="J122" s="9" t="s">
+      <c r="J122" s="9"/>
+      <c r="K122" s="9" t="s">
         <v>806</v>
       </c>
-      <c r="K122" s="9" t="s">
+      <c r="L122" s="9" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="123" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M122" s="42"/>
+    </row>
+    <row r="123" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A123" s="9" t="s">
         <v>807</v>
       </c>
@@ -19475,21 +20071,23 @@
       <c r="F123" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G123" s="9" t="s">
+      <c r="G123" s="9"/>
+      <c r="H123" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="H123" s="38">
+      <c r="I123" s="35">
         <v>2</v>
       </c>
-      <c r="I123" s="9"/>
-      <c r="J123" s="9" t="s">
+      <c r="J123" s="9"/>
+      <c r="K123" s="9" t="s">
         <v>809</v>
       </c>
-      <c r="K123" s="9" t="s">
+      <c r="L123" s="9" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="124" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M123" s="42"/>
+    </row>
+    <row r="124" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A124" s="9" t="s">
         <v>810</v>
       </c>
@@ -19508,21 +20106,23 @@
       <c r="F124" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G124" s="9" t="s">
+      <c r="G124" s="9"/>
+      <c r="H124" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H124" s="38">
+      <c r="I124" s="35">
         <v>3</v>
       </c>
-      <c r="I124" s="9"/>
-      <c r="J124" s="9" t="s">
+      <c r="J124" s="9"/>
+      <c r="K124" s="9" t="s">
         <v>812</v>
       </c>
-      <c r="K124" s="9" t="s">
+      <c r="L124" s="9" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="125" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M124" s="42"/>
+    </row>
+    <row r="125" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A125" s="9" t="s">
         <v>813</v>
       </c>
@@ -19541,21 +20141,23 @@
       <c r="F125" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G125" s="9" t="s">
+      <c r="G125" s="9"/>
+      <c r="H125" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H125" s="38">
+      <c r="I125" s="35">
         <v>3</v>
       </c>
-      <c r="I125" s="9"/>
-      <c r="J125" s="9" t="s">
+      <c r="J125" s="9"/>
+      <c r="K125" s="9" t="s">
         <v>815</v>
       </c>
-      <c r="K125" s="9" t="s">
+      <c r="L125" s="9" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="126" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M125" s="42"/>
+    </row>
+    <row r="126" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A126" s="9" t="s">
         <v>816</v>
       </c>
@@ -19574,21 +20176,23 @@
       <c r="F126" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G126" s="9" t="s">
+      <c r="G126" s="9"/>
+      <c r="H126" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H126" s="38">
+      <c r="I126" s="35">
         <v>2</v>
       </c>
-      <c r="I126" s="9"/>
-      <c r="J126" s="9" t="s">
+      <c r="J126" s="9"/>
+      <c r="K126" s="9" t="s">
         <v>818</v>
       </c>
-      <c r="K126" s="9" t="s">
+      <c r="L126" s="9" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="127" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M126" s="42"/>
+    </row>
+    <row r="127" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A127" s="9" t="s">
         <v>819</v>
       </c>
@@ -19607,21 +20211,23 @@
       <c r="F127" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G127" s="9" t="s">
+      <c r="G127" s="9"/>
+      <c r="H127" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="H127" s="38">
+      <c r="I127" s="35">
         <v>3</v>
       </c>
-      <c r="I127" s="9"/>
-      <c r="J127" s="9" t="s">
+      <c r="J127" s="9"/>
+      <c r="K127" s="9" t="s">
         <v>821</v>
       </c>
-      <c r="K127" s="9" t="s">
+      <c r="L127" s="9" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="128" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M127" s="42"/>
+    </row>
+    <row r="128" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A128" s="9" t="s">
         <v>822</v>
       </c>
@@ -19640,21 +20246,23 @@
       <c r="F128" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G128" s="9" t="s">
+      <c r="G128" s="9"/>
+      <c r="H128" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="H128" s="38">
+      <c r="I128" s="35">
         <v>3</v>
       </c>
-      <c r="I128" s="9"/>
-      <c r="J128" s="9" t="s">
+      <c r="J128" s="9"/>
+      <c r="K128" s="9" t="s">
         <v>824</v>
       </c>
-      <c r="K128" s="9" t="s">
+      <c r="L128" s="9" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="129" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M128" s="42"/>
+    </row>
+    <row r="129" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A129" s="9" t="s">
         <v>825</v>
       </c>
@@ -19673,21 +20281,23 @@
       <c r="F129" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G129" s="9" t="s">
+      <c r="G129" s="9"/>
+      <c r="H129" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="H129" s="38">
+      <c r="I129" s="35">
         <v>3</v>
       </c>
-      <c r="I129" s="9"/>
-      <c r="J129" s="9" t="s">
+      <c r="J129" s="9"/>
+      <c r="K129" s="9" t="s">
         <v>827</v>
       </c>
-      <c r="K129" s="9" t="s">
+      <c r="L129" s="9" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="130" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M129" s="42"/>
+    </row>
+    <row r="130" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A130" s="9" t="s">
         <v>828</v>
       </c>
@@ -19706,21 +20316,23 @@
       <c r="F130" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G130" s="9" t="s">
+      <c r="G130" s="9"/>
+      <c r="H130" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="H130" s="38">
+      <c r="I130" s="35">
         <v>2</v>
       </c>
-      <c r="I130" s="9"/>
-      <c r="J130" s="9" t="s">
+      <c r="J130" s="9"/>
+      <c r="K130" s="9" t="s">
         <v>830</v>
       </c>
-      <c r="K130" s="9" t="s">
+      <c r="L130" s="9" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="131" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M130" s="42"/>
+    </row>
+    <row r="131" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A131" s="9" t="s">
         <v>831</v>
       </c>
@@ -19739,21 +20351,23 @@
       <c r="F131" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G131" s="9" t="s">
+      <c r="G131" s="9"/>
+      <c r="H131" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="H131" s="38">
+      <c r="I131" s="35">
         <v>2</v>
       </c>
-      <c r="I131" s="9"/>
-      <c r="J131" s="9" t="s">
+      <c r="J131" s="9"/>
+      <c r="K131" s="9" t="s">
         <v>833</v>
       </c>
-      <c r="K131" s="9" t="s">
+      <c r="L131" s="9" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="132" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M131" s="42"/>
+    </row>
+    <row r="132" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A132" s="9" t="s">
         <v>834</v>
       </c>
@@ -19772,21 +20386,23 @@
       <c r="F132" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G132" s="9" t="s">
+      <c r="G132" s="9"/>
+      <c r="H132" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H132" s="38">
+      <c r="I132" s="35">
         <v>2</v>
       </c>
-      <c r="I132" s="9"/>
-      <c r="J132" s="9" t="s">
+      <c r="J132" s="9"/>
+      <c r="K132" s="9" t="s">
         <v>836</v>
       </c>
-      <c r="K132" s="9" t="s">
+      <c r="L132" s="9" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="133" spans="1:11" ht="32" hidden="1" customHeight="1">
+      <c r="M132" s="42"/>
+    </row>
+    <row r="133" spans="1:13" ht="32" hidden="1" customHeight="1">
       <c r="A133" s="9" t="s">
         <v>837</v>
       </c>
@@ -19805,21 +20421,23 @@
       <c r="F133" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G133" s="9" t="s">
+      <c r="G133" s="9"/>
+      <c r="H133" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H133" s="38">
+      <c r="I133" s="35">
         <v>2</v>
       </c>
-      <c r="I133" s="9"/>
-      <c r="J133" s="9" t="s">
+      <c r="J133" s="9"/>
+      <c r="K133" s="9" t="s">
         <v>839</v>
       </c>
-      <c r="K133" s="9" t="s">
+      <c r="L133" s="9" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="134" spans="1:11" ht="20" hidden="1" customHeight="1">
+      <c r="M133" s="42"/>
+    </row>
+    <row r="134" spans="1:13" ht="20" hidden="1" customHeight="1">
       <c r="A134" s="9" t="s">
         <v>840</v>
       </c>
@@ -19838,21 +20456,23 @@
       <c r="F134" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G134" s="9" t="s">
+      <c r="G134" s="9"/>
+      <c r="H134" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="H134" s="38">
+      <c r="I134" s="35">
         <v>2</v>
       </c>
-      <c r="I134" s="9"/>
-      <c r="J134" s="9" t="s">
+      <c r="J134" s="9"/>
+      <c r="K134" s="9" t="s">
         <v>842</v>
       </c>
-      <c r="K134" s="9" t="s">
+      <c r="L134" s="9" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="135" spans="1:11" ht="32" hidden="1" customHeight="1">
+      <c r="M134" s="42"/>
+    </row>
+    <row r="135" spans="1:13" ht="32" hidden="1" customHeight="1">
       <c r="A135" s="9" t="s">
         <v>843</v>
       </c>
@@ -19871,874 +20491,1846 @@
       <c r="F135" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G135" s="9" t="s">
+      <c r="G135" s="9"/>
+      <c r="H135" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="H135" s="38">
+      <c r="I135" s="35">
         <v>2</v>
       </c>
-      <c r="I135" s="9"/>
-      <c r="J135" s="9" t="s">
+      <c r="J135" s="9"/>
+      <c r="K135" s="9" t="s">
         <v>845</v>
       </c>
-      <c r="K135" s="9" t="s">
+      <c r="L135" s="9" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="136" spans="1:11">
+      <c r="M135" s="42"/>
+    </row>
+    <row r="136" spans="1:13">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
-      <c r="G136" s="1"/>
-      <c r="H136" s="30"/>
-      <c r="I136" s="1"/>
+      <c r="G136" s="9"/>
+      <c r="H136" s="1"/>
+      <c r="I136" s="30"/>
       <c r="J136" s="1"/>
       <c r="K136" s="1"/>
-    </row>
-    <row r="137" spans="1:11">
+      <c r="L136" s="1"/>
+      <c r="M136" s="1"/>
+    </row>
+    <row r="137" spans="1:13">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
-      <c r="G137" s="1"/>
-      <c r="H137" s="30"/>
-      <c r="I137" s="1"/>
+      <c r="G137" s="9"/>
+      <c r="H137" s="1"/>
+      <c r="I137" s="30"/>
       <c r="J137" s="1"/>
       <c r="K137" s="1"/>
-    </row>
-    <row r="138" spans="1:11">
+      <c r="L137" s="1"/>
+      <c r="M137" s="1"/>
+    </row>
+    <row r="138" spans="1:13">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
-      <c r="G138" s="1"/>
-      <c r="H138" s="30"/>
-      <c r="I138" s="1"/>
+      <c r="G138" s="9"/>
+      <c r="H138" s="1"/>
+      <c r="I138" s="30"/>
       <c r="J138" s="1"/>
       <c r="K138" s="1"/>
-    </row>
-    <row r="139" spans="1:11">
+      <c r="L138" s="1"/>
+      <c r="M138" s="1"/>
+    </row>
+    <row r="139" spans="1:13">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
-      <c r="G139" s="1"/>
-      <c r="H139" s="30"/>
-      <c r="I139" s="1"/>
+      <c r="G139" s="9"/>
+      <c r="H139" s="1"/>
+      <c r="I139" s="30"/>
       <c r="J139" s="1"/>
       <c r="K139" s="1"/>
-    </row>
-    <row r="140" spans="1:11">
+      <c r="L139" s="1"/>
+      <c r="M139" s="1"/>
+    </row>
+    <row r="140" spans="1:13">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
-      <c r="G140" s="1"/>
-      <c r="H140" s="30"/>
-      <c r="I140" s="1"/>
+      <c r="G140" s="9"/>
+      <c r="H140" s="1"/>
+      <c r="I140" s="30"/>
       <c r="J140" s="1"/>
       <c r="K140" s="1"/>
-    </row>
-    <row r="141" spans="1:11">
+      <c r="L140" s="1"/>
+      <c r="M140" s="1"/>
+    </row>
+    <row r="141" spans="1:13">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
-      <c r="G141" s="1"/>
-      <c r="H141" s="30"/>
-      <c r="I141" s="1"/>
+      <c r="G141" s="9"/>
+      <c r="H141" s="1"/>
+      <c r="I141" s="30"/>
       <c r="J141" s="1"/>
       <c r="K141" s="1"/>
-    </row>
-    <row r="142" spans="1:11">
+      <c r="L141" s="1"/>
+      <c r="M141" s="1"/>
+    </row>
+    <row r="142" spans="1:13">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
-      <c r="G142" s="1"/>
-      <c r="H142" s="30"/>
-      <c r="I142" s="1"/>
+      <c r="G142" s="9"/>
+      <c r="H142" s="1"/>
+      <c r="I142" s="30"/>
       <c r="J142" s="1"/>
       <c r="K142" s="1"/>
-    </row>
-    <row r="143" spans="1:11">
+      <c r="L142" s="1"/>
+      <c r="M142" s="1"/>
+    </row>
+    <row r="143" spans="1:13">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
-      <c r="G143" s="1"/>
-      <c r="H143" s="30"/>
-      <c r="I143" s="1"/>
+      <c r="G143" s="9"/>
+      <c r="H143" s="1"/>
+      <c r="I143" s="30"/>
       <c r="J143" s="1"/>
       <c r="K143" s="1"/>
-    </row>
-    <row r="144" spans="1:11">
+      <c r="L143" s="1"/>
+      <c r="M143" s="1"/>
+    </row>
+    <row r="144" spans="1:13">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
-      <c r="G144" s="1"/>
-      <c r="H144" s="30"/>
-      <c r="I144" s="1"/>
+      <c r="G144" s="9"/>
+      <c r="H144" s="1"/>
+      <c r="I144" s="30"/>
       <c r="J144" s="1"/>
       <c r="K144" s="1"/>
-    </row>
-    <row r="145" spans="1:11">
+      <c r="L144" s="1"/>
+      <c r="M144" s="1"/>
+    </row>
+    <row r="145" spans="1:13">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
-      <c r="G145" s="1"/>
-      <c r="H145" s="30"/>
-      <c r="I145" s="1"/>
+      <c r="G145" s="9"/>
+      <c r="H145" s="1"/>
+      <c r="I145" s="30"/>
       <c r="J145" s="1"/>
       <c r="K145" s="1"/>
-    </row>
-    <row r="146" spans="1:11">
+      <c r="L145" s="1"/>
+      <c r="M145" s="1"/>
+    </row>
+    <row r="146" spans="1:13">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
-      <c r="G146" s="1"/>
-      <c r="H146" s="30"/>
-      <c r="I146" s="1"/>
+      <c r="G146" s="9"/>
+      <c r="H146" s="1"/>
+      <c r="I146" s="30"/>
       <c r="J146" s="1"/>
       <c r="K146" s="1"/>
-    </row>
-    <row r="147" spans="1:11">
+      <c r="L146" s="1"/>
+      <c r="M146" s="1"/>
+    </row>
+    <row r="147" spans="1:13">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
-      <c r="G147" s="1"/>
-      <c r="H147" s="30"/>
-      <c r="I147" s="1"/>
+      <c r="G147" s="9"/>
+      <c r="H147" s="1"/>
+      <c r="I147" s="30"/>
       <c r="J147" s="1"/>
       <c r="K147" s="1"/>
-    </row>
-    <row r="148" spans="1:11">
+      <c r="L147" s="1"/>
+      <c r="M147" s="1"/>
+    </row>
+    <row r="148" spans="1:13">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
-      <c r="G148" s="1"/>
-      <c r="H148" s="30"/>
-      <c r="I148" s="1"/>
+      <c r="G148" s="9"/>
+      <c r="H148" s="1"/>
+      <c r="I148" s="30"/>
       <c r="J148" s="1"/>
       <c r="K148" s="1"/>
-    </row>
-    <row r="149" spans="1:11">
+      <c r="L148" s="1"/>
+      <c r="M148" s="1"/>
+    </row>
+    <row r="149" spans="1:13">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
-      <c r="G149" s="1"/>
-      <c r="H149" s="30"/>
-      <c r="I149" s="1"/>
+      <c r="G149" s="9"/>
+      <c r="H149" s="1"/>
+      <c r="I149" s="30"/>
       <c r="J149" s="1"/>
       <c r="K149" s="1"/>
-    </row>
-    <row r="150" spans="1:11">
+      <c r="L149" s="1"/>
+      <c r="M149" s="1"/>
+    </row>
+    <row r="150" spans="1:13">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
-      <c r="G150" s="1"/>
-      <c r="H150" s="30"/>
-      <c r="I150" s="1"/>
+      <c r="G150" s="9"/>
+      <c r="H150" s="1"/>
+      <c r="I150" s="30"/>
       <c r="J150" s="1"/>
       <c r="K150" s="1"/>
-    </row>
-    <row r="151" spans="1:11">
+      <c r="L150" s="1"/>
+      <c r="M150" s="1"/>
+    </row>
+    <row r="151" spans="1:13">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
-      <c r="G151" s="1"/>
-      <c r="H151" s="30"/>
-      <c r="I151" s="1"/>
+      <c r="G151" s="9"/>
+      <c r="H151" s="1"/>
+      <c r="I151" s="30"/>
       <c r="J151" s="1"/>
       <c r="K151" s="1"/>
-    </row>
-    <row r="152" spans="1:11">
+      <c r="L151" s="1"/>
+      <c r="M151" s="1"/>
+    </row>
+    <row r="152" spans="1:13">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
-      <c r="G152" s="1"/>
-      <c r="H152" s="30"/>
-      <c r="I152" s="1"/>
+      <c r="G152" s="9"/>
+      <c r="H152" s="1"/>
+      <c r="I152" s="30"/>
       <c r="J152" s="1"/>
       <c r="K152" s="1"/>
-    </row>
-    <row r="153" spans="1:11">
+      <c r="L152" s="1"/>
+      <c r="M152" s="1"/>
+    </row>
+    <row r="153" spans="1:13">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
-      <c r="G153" s="1"/>
-      <c r="H153" s="30"/>
-      <c r="I153" s="1"/>
+      <c r="G153" s="9"/>
+      <c r="H153" s="1"/>
+      <c r="I153" s="30"/>
       <c r="J153" s="1"/>
       <c r="K153" s="1"/>
-    </row>
-    <row r="154" spans="1:11">
+      <c r="L153" s="1"/>
+      <c r="M153" s="1"/>
+    </row>
+    <row r="154" spans="1:13">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
-      <c r="G154" s="1"/>
-      <c r="H154" s="30"/>
-      <c r="I154" s="1"/>
+      <c r="G154" s="9"/>
+      <c r="H154" s="1"/>
+      <c r="I154" s="30"/>
       <c r="J154" s="1"/>
       <c r="K154" s="1"/>
-    </row>
-    <row r="155" spans="1:11">
+      <c r="L154" s="1"/>
+      <c r="M154" s="1"/>
+    </row>
+    <row r="155" spans="1:13">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
-      <c r="G155" s="1"/>
-      <c r="H155" s="30"/>
-      <c r="I155" s="1"/>
+      <c r="G155" s="9"/>
+      <c r="H155" s="1"/>
+      <c r="I155" s="30"/>
       <c r="J155" s="1"/>
       <c r="K155" s="1"/>
-    </row>
-    <row r="156" spans="1:11">
+      <c r="L155" s="1"/>
+      <c r="M155" s="1"/>
+    </row>
+    <row r="156" spans="1:13">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
-      <c r="G156" s="1"/>
-      <c r="H156" s="30"/>
-      <c r="I156" s="1"/>
+      <c r="G156" s="9"/>
+      <c r="H156" s="1"/>
+      <c r="I156" s="30"/>
       <c r="J156" s="1"/>
       <c r="K156" s="1"/>
-    </row>
-    <row r="157" spans="1:11">
+      <c r="L156" s="1"/>
+      <c r="M156" s="1"/>
+    </row>
+    <row r="157" spans="1:13">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
-      <c r="G157" s="1"/>
-      <c r="H157" s="30"/>
-      <c r="I157" s="1"/>
+      <c r="G157" s="9"/>
+      <c r="H157" s="1"/>
+      <c r="I157" s="30"/>
       <c r="J157" s="1"/>
       <c r="K157" s="1"/>
-    </row>
-    <row r="158" spans="1:11">
+      <c r="L157" s="1"/>
+      <c r="M157" s="1"/>
+    </row>
+    <row r="158" spans="1:13">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
-      <c r="G158" s="1"/>
-      <c r="H158" s="30"/>
-      <c r="I158" s="1"/>
+      <c r="G158" s="9"/>
+      <c r="H158" s="1"/>
+      <c r="I158" s="30"/>
       <c r="J158" s="1"/>
       <c r="K158" s="1"/>
-    </row>
-    <row r="159" spans="1:11">
+      <c r="L158" s="1"/>
+      <c r="M158" s="1"/>
+    </row>
+    <row r="159" spans="1:13">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
-      <c r="G159" s="1"/>
-      <c r="H159" s="30"/>
-      <c r="I159" s="1"/>
+      <c r="G159" s="9"/>
+      <c r="H159" s="1"/>
+      <c r="I159" s="30"/>
       <c r="J159" s="1"/>
       <c r="K159" s="1"/>
-    </row>
-    <row r="160" spans="1:11">
+      <c r="L159" s="1"/>
+      <c r="M159" s="1"/>
+    </row>
+    <row r="160" spans="1:13">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
-      <c r="G160" s="1"/>
-      <c r="H160" s="30"/>
-      <c r="I160" s="1"/>
+      <c r="G160" s="9"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="30"/>
       <c r="J160" s="1"/>
       <c r="K160" s="1"/>
-    </row>
-    <row r="161" spans="1:11">
+      <c r="L160" s="1"/>
+      <c r="M160" s="1"/>
+    </row>
+    <row r="161" spans="1:13">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
-      <c r="G161" s="1"/>
-      <c r="H161" s="30"/>
-      <c r="I161" s="1"/>
+      <c r="G161" s="9"/>
+      <c r="H161" s="1"/>
+      <c r="I161" s="30"/>
       <c r="J161" s="1"/>
       <c r="K161" s="1"/>
-    </row>
-    <row r="162" spans="1:11">
+      <c r="L161" s="1"/>
+      <c r="M161" s="1"/>
+    </row>
+    <row r="162" spans="1:13">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
-      <c r="G162" s="1"/>
-      <c r="H162" s="30"/>
-      <c r="I162" s="1"/>
+      <c r="G162" s="9"/>
+      <c r="H162" s="1"/>
+      <c r="I162" s="30"/>
       <c r="J162" s="1"/>
       <c r="K162" s="1"/>
-    </row>
-    <row r="163" spans="1:11">
+      <c r="L162" s="1"/>
+      <c r="M162" s="1"/>
+    </row>
+    <row r="163" spans="1:13">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
-      <c r="G163" s="1"/>
-      <c r="H163" s="30"/>
-      <c r="I163" s="1"/>
+      <c r="G163" s="9"/>
+      <c r="H163" s="1"/>
+      <c r="I163" s="30"/>
       <c r="J163" s="1"/>
       <c r="K163" s="1"/>
-    </row>
-    <row r="164" spans="1:11">
+      <c r="L163" s="1"/>
+      <c r="M163" s="1"/>
+    </row>
+    <row r="164" spans="1:13">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
-      <c r="G164" s="1"/>
-      <c r="H164" s="30"/>
-      <c r="I164" s="1"/>
+      <c r="G164" s="9"/>
+      <c r="H164" s="1"/>
+      <c r="I164" s="30"/>
       <c r="J164" s="1"/>
       <c r="K164" s="1"/>
-    </row>
-    <row r="165" spans="1:11">
+      <c r="L164" s="1"/>
+      <c r="M164" s="1"/>
+    </row>
+    <row r="165" spans="1:13">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
-      <c r="G165" s="1"/>
-      <c r="H165" s="30"/>
-      <c r="I165" s="1"/>
+      <c r="G165" s="9"/>
+      <c r="H165" s="1"/>
+      <c r="I165" s="30"/>
       <c r="J165" s="1"/>
       <c r="K165" s="1"/>
-    </row>
-    <row r="166" spans="1:11">
+      <c r="L165" s="1"/>
+      <c r="M165" s="1"/>
+    </row>
+    <row r="166" spans="1:13">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
-      <c r="G166" s="1"/>
-      <c r="H166" s="30"/>
-      <c r="I166" s="1"/>
+      <c r="G166" s="9"/>
+      <c r="H166" s="1"/>
+      <c r="I166" s="30"/>
       <c r="J166" s="1"/>
       <c r="K166" s="1"/>
-    </row>
-    <row r="167" spans="1:11">
+      <c r="L166" s="1"/>
+      <c r="M166" s="1"/>
+    </row>
+    <row r="167" spans="1:13">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
-      <c r="G167" s="1"/>
-      <c r="H167" s="30"/>
-      <c r="I167" s="1"/>
+      <c r="G167" s="9"/>
+      <c r="H167" s="1"/>
+      <c r="I167" s="30"/>
       <c r="J167" s="1"/>
       <c r="K167" s="1"/>
-    </row>
-    <row r="168" spans="1:11">
+      <c r="L167" s="1"/>
+      <c r="M167" s="1"/>
+    </row>
+    <row r="168" spans="1:13">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
-      <c r="G168" s="1"/>
-      <c r="H168" s="30"/>
-      <c r="I168" s="1"/>
+      <c r="G168" s="9"/>
+      <c r="H168" s="1"/>
+      <c r="I168" s="30"/>
       <c r="J168" s="1"/>
       <c r="K168" s="1"/>
-    </row>
-    <row r="169" spans="1:11">
+      <c r="L168" s="1"/>
+      <c r="M168" s="1"/>
+    </row>
+    <row r="169" spans="1:13">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
-      <c r="G169" s="1"/>
-      <c r="H169" s="30"/>
-      <c r="I169" s="1"/>
+      <c r="G169" s="9"/>
+      <c r="H169" s="1"/>
+      <c r="I169" s="30"/>
       <c r="J169" s="1"/>
       <c r="K169" s="1"/>
-    </row>
-    <row r="170" spans="1:11">
+      <c r="L169" s="1"/>
+      <c r="M169" s="1"/>
+    </row>
+    <row r="170" spans="1:13">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
       <c r="D170" s="1"/>
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
-      <c r="G170" s="1"/>
-      <c r="H170" s="30"/>
-      <c r="I170" s="1"/>
+      <c r="G170" s="9"/>
+      <c r="H170" s="1"/>
+      <c r="I170" s="30"/>
       <c r="J170" s="1"/>
       <c r="K170" s="1"/>
-    </row>
-    <row r="171" spans="1:11">
+      <c r="L170" s="1"/>
+      <c r="M170" s="1"/>
+    </row>
+    <row r="171" spans="1:13">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
       <c r="D171" s="1"/>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
-      <c r="G171" s="1"/>
-      <c r="H171" s="30"/>
-      <c r="I171" s="1"/>
+      <c r="G171" s="9"/>
+      <c r="H171" s="1"/>
+      <c r="I171" s="30"/>
       <c r="J171" s="1"/>
       <c r="K171" s="1"/>
-    </row>
-    <row r="172" spans="1:11">
+      <c r="L171" s="1"/>
+      <c r="M171" s="1"/>
+    </row>
+    <row r="172" spans="1:13">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
       <c r="D172" s="1"/>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
-      <c r="G172" s="1"/>
-      <c r="H172" s="30"/>
-      <c r="I172" s="1"/>
+      <c r="G172" s="9"/>
+      <c r="H172" s="1"/>
+      <c r="I172" s="30"/>
       <c r="J172" s="1"/>
       <c r="K172" s="1"/>
-    </row>
-    <row r="173" spans="1:11">
+      <c r="L172" s="1"/>
+      <c r="M172" s="1"/>
+    </row>
+    <row r="173" spans="1:13">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
       <c r="D173" s="1"/>
       <c r="E173" s="1"/>
       <c r="F173" s="1"/>
-      <c r="G173" s="1"/>
-      <c r="H173" s="30"/>
-      <c r="I173" s="1"/>
+      <c r="G173" s="9"/>
+      <c r="H173" s="1"/>
+      <c r="I173" s="30"/>
       <c r="J173" s="1"/>
       <c r="K173" s="1"/>
-    </row>
-    <row r="174" spans="1:11">
+      <c r="L173" s="1"/>
+      <c r="M173" s="1"/>
+    </row>
+    <row r="174" spans="1:13">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
       <c r="D174" s="1"/>
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
-      <c r="G174" s="1"/>
-      <c r="H174" s="30"/>
-      <c r="I174" s="1"/>
+      <c r="G174" s="9"/>
+      <c r="H174" s="1"/>
+      <c r="I174" s="30"/>
       <c r="J174" s="1"/>
       <c r="K174" s="1"/>
-    </row>
-    <row r="175" spans="1:11">
+      <c r="L174" s="1"/>
+      <c r="M174" s="1"/>
+    </row>
+    <row r="175" spans="1:13">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
       <c r="D175" s="1"/>
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
-      <c r="G175" s="1"/>
-      <c r="H175" s="30"/>
-      <c r="I175" s="1"/>
+      <c r="G175" s="9"/>
+      <c r="H175" s="1"/>
+      <c r="I175" s="30"/>
       <c r="J175" s="1"/>
       <c r="K175" s="1"/>
-    </row>
-    <row r="176" spans="1:11">
+      <c r="L175" s="1"/>
+      <c r="M175" s="1"/>
+    </row>
+    <row r="176" spans="1:13">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
       <c r="D176" s="1"/>
       <c r="E176" s="1"/>
       <c r="F176" s="1"/>
-      <c r="G176" s="1"/>
-      <c r="H176" s="30"/>
-      <c r="I176" s="1"/>
+      <c r="G176" s="9"/>
+      <c r="H176" s="1"/>
+      <c r="I176" s="30"/>
       <c r="J176" s="1"/>
       <c r="K176" s="1"/>
-    </row>
-    <row r="177" spans="1:11">
+      <c r="L176" s="1"/>
+      <c r="M176" s="1"/>
+    </row>
+    <row r="177" spans="1:13">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
       <c r="D177" s="1"/>
       <c r="E177" s="1"/>
       <c r="F177" s="1"/>
-      <c r="G177" s="1"/>
-      <c r="H177" s="30"/>
-      <c r="I177" s="1"/>
+      <c r="G177" s="9"/>
+      <c r="H177" s="1"/>
+      <c r="I177" s="30"/>
       <c r="J177" s="1"/>
       <c r="K177" s="1"/>
-    </row>
-    <row r="178" spans="1:11">
+      <c r="L177" s="1"/>
+      <c r="M177" s="1"/>
+    </row>
+    <row r="178" spans="1:13">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
       <c r="D178" s="1"/>
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
-      <c r="G178" s="1"/>
-      <c r="H178" s="30"/>
-      <c r="I178" s="1"/>
+      <c r="G178" s="9"/>
+      <c r="H178" s="1"/>
+      <c r="I178" s="30"/>
       <c r="J178" s="1"/>
       <c r="K178" s="1"/>
-    </row>
-    <row r="179" spans="1:11">
+      <c r="L178" s="1"/>
+      <c r="M178" s="1"/>
+    </row>
+    <row r="179" spans="1:13">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
       <c r="D179" s="1"/>
       <c r="E179" s="1"/>
       <c r="F179" s="1"/>
-      <c r="G179" s="1"/>
-      <c r="H179" s="30"/>
-      <c r="I179" s="1"/>
+      <c r="G179" s="9"/>
+      <c r="H179" s="1"/>
+      <c r="I179" s="30"/>
       <c r="J179" s="1"/>
       <c r="K179" s="1"/>
-    </row>
-    <row r="180" spans="1:11">
+      <c r="L179" s="1"/>
+      <c r="M179" s="1"/>
+    </row>
+    <row r="180" spans="1:13">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
       <c r="D180" s="1"/>
       <c r="E180" s="1"/>
       <c r="F180" s="1"/>
-      <c r="G180" s="1"/>
-      <c r="H180" s="30"/>
-      <c r="I180" s="1"/>
+      <c r="G180" s="9"/>
+      <c r="H180" s="1"/>
+      <c r="I180" s="30"/>
       <c r="J180" s="1"/>
       <c r="K180" s="1"/>
-    </row>
-    <row r="181" spans="1:11">
+      <c r="L180" s="1"/>
+      <c r="M180" s="1"/>
+    </row>
+    <row r="181" spans="1:13">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
       <c r="F181" s="1"/>
-      <c r="G181" s="1"/>
-      <c r="H181" s="30"/>
-      <c r="I181" s="1"/>
+      <c r="G181" s="9"/>
+      <c r="H181" s="1"/>
+      <c r="I181" s="30"/>
       <c r="J181" s="1"/>
       <c r="K181" s="1"/>
-    </row>
-    <row r="182" spans="1:11">
+      <c r="L181" s="1"/>
+      <c r="M181" s="1"/>
+    </row>
+    <row r="182" spans="1:13">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
-      <c r="G182" s="1"/>
-      <c r="H182" s="30"/>
-      <c r="I182" s="1"/>
+      <c r="G182" s="9"/>
+      <c r="H182" s="1"/>
+      <c r="I182" s="30"/>
       <c r="J182" s="1"/>
       <c r="K182" s="1"/>
-    </row>
-    <row r="183" spans="1:11">
+      <c r="L182" s="1"/>
+      <c r="M182" s="1"/>
+    </row>
+    <row r="183" spans="1:13">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
-      <c r="G183" s="1"/>
-      <c r="H183" s="30"/>
-      <c r="I183" s="1"/>
+      <c r="G183" s="9"/>
+      <c r="H183" s="1"/>
+      <c r="I183" s="30"/>
       <c r="J183" s="1"/>
       <c r="K183" s="1"/>
-    </row>
-    <row r="184" spans="1:11">
+      <c r="L183" s="1"/>
+      <c r="M183" s="1"/>
+    </row>
+    <row r="184" spans="1:13">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
       <c r="F184" s="1"/>
-      <c r="G184" s="1"/>
-      <c r="H184" s="30"/>
-      <c r="I184" s="1"/>
+      <c r="G184" s="9"/>
+      <c r="H184" s="1"/>
+      <c r="I184" s="30"/>
       <c r="J184" s="1"/>
       <c r="K184" s="1"/>
-    </row>
-    <row r="185" spans="1:11">
+      <c r="L184" s="1"/>
+      <c r="M184" s="1"/>
+    </row>
+    <row r="185" spans="1:13">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
-      <c r="G185" s="1"/>
-      <c r="H185" s="30"/>
-      <c r="I185" s="1"/>
+      <c r="G185" s="9"/>
+      <c r="H185" s="1"/>
+      <c r="I185" s="30"/>
       <c r="J185" s="1"/>
       <c r="K185" s="1"/>
-    </row>
-    <row r="186" spans="1:11">
+      <c r="L185" s="1"/>
+      <c r="M185" s="1"/>
+    </row>
+    <row r="186" spans="1:13">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
-      <c r="G186" s="1"/>
-      <c r="H186" s="30"/>
-      <c r="I186" s="1"/>
+      <c r="G186" s="9"/>
+      <c r="H186" s="1"/>
+      <c r="I186" s="30"/>
       <c r="J186" s="1"/>
       <c r="K186" s="1"/>
-    </row>
-    <row r="187" spans="1:11">
+      <c r="L186" s="1"/>
+      <c r="M186" s="1"/>
+    </row>
+    <row r="187" spans="1:13">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
       <c r="F187" s="1"/>
-      <c r="G187" s="1"/>
-      <c r="H187" s="30"/>
-      <c r="I187" s="1"/>
+      <c r="G187" s="9"/>
+      <c r="H187" s="1"/>
+      <c r="I187" s="30"/>
       <c r="J187" s="1"/>
       <c r="K187" s="1"/>
-    </row>
-    <row r="188" spans="1:11">
+      <c r="L187" s="1"/>
+      <c r="M187" s="1"/>
+    </row>
+    <row r="188" spans="1:13">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
       <c r="F188" s="1"/>
-      <c r="G188" s="1"/>
-      <c r="H188" s="30"/>
-      <c r="I188" s="1"/>
+      <c r="G188" s="9"/>
+      <c r="H188" s="1"/>
+      <c r="I188" s="30"/>
       <c r="J188" s="1"/>
       <c r="K188" s="1"/>
-    </row>
-    <row r="189" spans="1:11">
+      <c r="L188" s="1"/>
+      <c r="M188" s="1"/>
+    </row>
+    <row r="189" spans="1:13">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
-      <c r="G189" s="1"/>
-      <c r="H189" s="30"/>
-      <c r="I189" s="1"/>
+      <c r="G189" s="9"/>
+      <c r="H189" s="1"/>
+      <c r="I189" s="30"/>
       <c r="J189" s="1"/>
       <c r="K189" s="1"/>
-    </row>
-    <row r="190" spans="1:11">
+      <c r="L189" s="1"/>
+      <c r="M189" s="1"/>
+    </row>
+    <row r="190" spans="1:13">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
-      <c r="G190" s="1"/>
-      <c r="H190" s="30"/>
-      <c r="I190" s="1"/>
+      <c r="G190" s="9"/>
+      <c r="H190" s="1"/>
+      <c r="I190" s="30"/>
       <c r="J190" s="1"/>
       <c r="K190" s="1"/>
-    </row>
-    <row r="191" spans="1:11">
+      <c r="L190" s="1"/>
+      <c r="M190" s="1"/>
+    </row>
+    <row r="191" spans="1:13">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
       <c r="F191" s="1"/>
-      <c r="G191" s="1"/>
-      <c r="H191" s="30"/>
-      <c r="I191" s="1"/>
+      <c r="G191" s="9"/>
+      <c r="H191" s="1"/>
+      <c r="I191" s="30"/>
       <c r="J191" s="1"/>
       <c r="K191" s="1"/>
-    </row>
-    <row r="192" spans="1:11">
+      <c r="L191" s="1"/>
+      <c r="M191" s="1"/>
+    </row>
+    <row r="192" spans="1:13">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
-      <c r="G192" s="1"/>
-      <c r="H192" s="30"/>
-      <c r="I192" s="1"/>
+      <c r="G192" s="9"/>
+      <c r="H192" s="1"/>
+      <c r="I192" s="30"/>
       <c r="J192" s="1"/>
       <c r="K192" s="1"/>
-    </row>
-    <row r="193" spans="1:11">
+      <c r="L192" s="1"/>
+      <c r="M192" s="1"/>
+    </row>
+    <row r="193" spans="1:13">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
-      <c r="G193" s="1"/>
-      <c r="H193" s="30"/>
-      <c r="I193" s="1"/>
+      <c r="G193" s="9"/>
+      <c r="H193" s="1"/>
+      <c r="I193" s="30"/>
       <c r="J193" s="1"/>
       <c r="K193" s="1"/>
-    </row>
-    <row r="194" spans="1:11">
+      <c r="L193" s="1"/>
+      <c r="M193" s="1"/>
+    </row>
+    <row r="194" spans="1:13">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
-      <c r="G194" s="1"/>
-      <c r="H194" s="30"/>
-      <c r="I194" s="1"/>
+      <c r="G194" s="9"/>
+      <c r="H194" s="1"/>
+      <c r="I194" s="30"/>
       <c r="J194" s="1"/>
       <c r="K194" s="1"/>
-    </row>
-    <row r="195" spans="1:11">
+      <c r="L194" s="1"/>
+      <c r="M194" s="1"/>
+    </row>
+    <row r="195" spans="1:13">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
-      <c r="G195" s="1"/>
-      <c r="H195" s="30"/>
-      <c r="I195" s="1"/>
+      <c r="G195" s="9"/>
+      <c r="H195" s="1"/>
+      <c r="I195" s="30"/>
       <c r="J195" s="1"/>
       <c r="K195" s="1"/>
-    </row>
-    <row r="196" spans="1:11">
+      <c r="L195" s="1"/>
+      <c r="M195" s="1"/>
+    </row>
+    <row r="196" spans="1:13">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
       <c r="F196" s="1"/>
-      <c r="G196" s="1"/>
-      <c r="H196" s="30"/>
-      <c r="I196" s="1"/>
+      <c r="G196" s="9"/>
+      <c r="H196" s="1"/>
+      <c r="I196" s="30"/>
       <c r="J196" s="1"/>
       <c r="K196" s="1"/>
-    </row>
-    <row r="197" spans="1:11">
+      <c r="L196" s="1"/>
+      <c r="M196" s="1"/>
+    </row>
+    <row r="197" spans="1:13">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
-      <c r="G197" s="1"/>
-      <c r="H197" s="30"/>
-      <c r="I197" s="1"/>
+      <c r="G197" s="9"/>
+      <c r="H197" s="1"/>
+      <c r="I197" s="30"/>
       <c r="J197" s="1"/>
       <c r="K197" s="1"/>
-    </row>
-    <row r="198" spans="1:11">
+      <c r="L197" s="1"/>
+      <c r="M197" s="1"/>
+    </row>
+    <row r="198" spans="1:13">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
-      <c r="G198" s="1"/>
-      <c r="H198" s="30"/>
-      <c r="I198" s="1"/>
+      <c r="G198" s="9"/>
+      <c r="H198" s="1"/>
+      <c r="I198" s="30"/>
       <c r="J198" s="1"/>
       <c r="K198" s="1"/>
-    </row>
-    <row r="199" spans="1:11">
+      <c r="L198" s="1"/>
+      <c r="M198" s="1"/>
+    </row>
+    <row r="199" spans="1:13">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
-      <c r="G199" s="1"/>
-      <c r="H199" s="30"/>
-      <c r="I199" s="1"/>
+      <c r="G199" s="9"/>
+      <c r="H199" s="1"/>
+      <c r="I199" s="30"/>
       <c r="J199" s="1"/>
       <c r="K199" s="1"/>
-    </row>
-    <row r="200" spans="1:11">
+      <c r="L199" s="1"/>
+      <c r="M199" s="1"/>
+    </row>
+    <row r="200" spans="1:13">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
       <c r="F200" s="1"/>
-      <c r="G200" s="1"/>
-      <c r="H200" s="30"/>
-      <c r="I200" s="1"/>
+      <c r="G200" s="9"/>
+      <c r="H200" s="1"/>
+      <c r="I200" s="30"/>
       <c r="J200" s="1"/>
       <c r="K200" s="1"/>
+      <c r="L200" s="1"/>
+      <c r="M200" s="1"/>
+    </row>
+    <row r="201" spans="1:13">
+      <c r="G201" s="9"/>
+    </row>
+    <row r="202" spans="1:13">
+      <c r="G202" s="9"/>
+    </row>
+    <row r="203" spans="1:13">
+      <c r="G203" s="9"/>
+    </row>
+    <row r="204" spans="1:13">
+      <c r="G204" s="9"/>
+    </row>
+    <row r="205" spans="1:13">
+      <c r="G205" s="9"/>
+    </row>
+    <row r="206" spans="1:13">
+      <c r="G206" s="9"/>
+    </row>
+    <row r="207" spans="1:13">
+      <c r="G207" s="9"/>
+    </row>
+    <row r="208" spans="1:13">
+      <c r="G208" s="9"/>
+    </row>
+    <row r="209" spans="7:7">
+      <c r="G209" s="9"/>
+    </row>
+    <row r="210" spans="7:7">
+      <c r="G210" s="9"/>
+    </row>
+    <row r="211" spans="7:7">
+      <c r="G211" s="9"/>
+    </row>
+    <row r="212" spans="7:7">
+      <c r="G212" s="9"/>
+    </row>
+    <row r="213" spans="7:7">
+      <c r="G213" s="9"/>
+    </row>
+    <row r="214" spans="7:7">
+      <c r="G214" s="9"/>
+    </row>
+    <row r="215" spans="7:7">
+      <c r="G215" s="9"/>
+    </row>
+    <row r="216" spans="7:7">
+      <c r="G216" s="9"/>
+    </row>
+    <row r="217" spans="7:7">
+      <c r="G217" s="9"/>
+    </row>
+    <row r="218" spans="7:7">
+      <c r="G218" s="9"/>
+    </row>
+    <row r="219" spans="7:7">
+      <c r="G219" s="9"/>
+    </row>
+    <row r="220" spans="7:7">
+      <c r="G220" s="9"/>
+    </row>
+    <row r="221" spans="7:7">
+      <c r="G221" s="9"/>
+    </row>
+    <row r="222" spans="7:7">
+      <c r="G222" s="9"/>
+    </row>
+    <row r="223" spans="7:7">
+      <c r="G223" s="9"/>
+    </row>
+    <row r="224" spans="7:7">
+      <c r="G224" s="9"/>
+    </row>
+    <row r="225" spans="7:7">
+      <c r="G225" s="9"/>
+    </row>
+    <row r="226" spans="7:7">
+      <c r="G226" s="9"/>
+    </row>
+    <row r="227" spans="7:7">
+      <c r="G227" s="9"/>
+    </row>
+    <row r="228" spans="7:7">
+      <c r="G228" s="9"/>
+    </row>
+    <row r="229" spans="7:7">
+      <c r="G229" s="9"/>
+    </row>
+    <row r="230" spans="7:7">
+      <c r="G230" s="9"/>
+    </row>
+    <row r="231" spans="7:7">
+      <c r="G231" s="9"/>
+    </row>
+    <row r="232" spans="7:7">
+      <c r="G232" s="9"/>
+    </row>
+    <row r="233" spans="7:7">
+      <c r="G233" s="9"/>
+    </row>
+    <row r="234" spans="7:7">
+      <c r="G234" s="9"/>
+    </row>
+    <row r="235" spans="7:7">
+      <c r="G235" s="9"/>
+    </row>
+    <row r="236" spans="7:7">
+      <c r="G236" s="9"/>
+    </row>
+    <row r="237" spans="7:7">
+      <c r="G237" s="9"/>
+    </row>
+    <row r="238" spans="7:7">
+      <c r="G238" s="9"/>
+    </row>
+    <row r="239" spans="7:7">
+      <c r="G239" s="9"/>
+    </row>
+    <row r="240" spans="7:7">
+      <c r="G240" s="9"/>
+    </row>
+    <row r="241" spans="7:7">
+      <c r="G241" s="9"/>
+    </row>
+    <row r="242" spans="7:7">
+      <c r="G242" s="9"/>
+    </row>
+    <row r="243" spans="7:7">
+      <c r="G243" s="9"/>
+    </row>
+    <row r="244" spans="7:7">
+      <c r="G244" s="9"/>
+    </row>
+    <row r="245" spans="7:7">
+      <c r="G245" s="9"/>
+    </row>
+    <row r="246" spans="7:7">
+      <c r="G246" s="9"/>
+    </row>
+    <row r="247" spans="7:7">
+      <c r="G247" s="9"/>
+    </row>
+    <row r="248" spans="7:7">
+      <c r="G248" s="9"/>
+    </row>
+    <row r="249" spans="7:7">
+      <c r="G249" s="9"/>
+    </row>
+    <row r="250" spans="7:7">
+      <c r="G250" s="9"/>
+    </row>
+    <row r="251" spans="7:7">
+      <c r="G251" s="9"/>
+    </row>
+    <row r="252" spans="7:7">
+      <c r="G252" s="9"/>
+    </row>
+    <row r="253" spans="7:7">
+      <c r="G253" s="9"/>
+    </row>
+    <row r="254" spans="7:7">
+      <c r="G254" s="9"/>
+    </row>
+    <row r="255" spans="7:7">
+      <c r="G255" s="9"/>
+    </row>
+    <row r="256" spans="7:7">
+      <c r="G256" s="9"/>
+    </row>
+    <row r="257" spans="7:7">
+      <c r="G257" s="9"/>
+    </row>
+    <row r="258" spans="7:7">
+      <c r="G258" s="9"/>
+    </row>
+    <row r="259" spans="7:7">
+      <c r="G259" s="9"/>
+    </row>
+    <row r="260" spans="7:7">
+      <c r="G260" s="9"/>
+    </row>
+    <row r="261" spans="7:7">
+      <c r="G261" s="9"/>
+    </row>
+    <row r="262" spans="7:7">
+      <c r="G262" s="9"/>
+    </row>
+    <row r="263" spans="7:7">
+      <c r="G263" s="9"/>
+    </row>
+    <row r="264" spans="7:7">
+      <c r="G264" s="9"/>
+    </row>
+    <row r="265" spans="7:7">
+      <c r="G265" s="9"/>
+    </row>
+    <row r="266" spans="7:7">
+      <c r="G266" s="9"/>
+    </row>
+    <row r="267" spans="7:7">
+      <c r="G267" s="9"/>
+    </row>
+    <row r="268" spans="7:7">
+      <c r="G268" s="9"/>
+    </row>
+    <row r="269" spans="7:7">
+      <c r="G269" s="9"/>
+    </row>
+    <row r="270" spans="7:7">
+      <c r="G270" s="9"/>
+    </row>
+    <row r="271" spans="7:7">
+      <c r="G271" s="9"/>
+    </row>
+    <row r="272" spans="7:7">
+      <c r="G272" s="9"/>
+    </row>
+    <row r="273" spans="7:7">
+      <c r="G273" s="9"/>
+    </row>
+    <row r="274" spans="7:7">
+      <c r="G274" s="9"/>
+    </row>
+    <row r="275" spans="7:7">
+      <c r="G275" s="9"/>
+    </row>
+    <row r="276" spans="7:7">
+      <c r="G276" s="9"/>
+    </row>
+    <row r="277" spans="7:7">
+      <c r="G277" s="9"/>
+    </row>
+    <row r="278" spans="7:7">
+      <c r="G278" s="9"/>
+    </row>
+    <row r="279" spans="7:7">
+      <c r="G279" s="9"/>
+    </row>
+    <row r="280" spans="7:7">
+      <c r="G280" s="9"/>
+    </row>
+    <row r="281" spans="7:7">
+      <c r="G281" s="9"/>
+    </row>
+    <row r="282" spans="7:7">
+      <c r="G282" s="9"/>
+    </row>
+    <row r="283" spans="7:7">
+      <c r="G283" s="9"/>
+    </row>
+    <row r="284" spans="7:7">
+      <c r="G284" s="9"/>
+    </row>
+    <row r="285" spans="7:7">
+      <c r="G285" s="9"/>
+    </row>
+    <row r="286" spans="7:7">
+      <c r="G286" s="9"/>
+    </row>
+    <row r="287" spans="7:7">
+      <c r="G287" s="9"/>
+    </row>
+    <row r="288" spans="7:7">
+      <c r="G288" s="9"/>
+    </row>
+    <row r="289" spans="7:7">
+      <c r="G289" s="9"/>
+    </row>
+    <row r="290" spans="7:7">
+      <c r="G290" s="9"/>
+    </row>
+    <row r="291" spans="7:7">
+      <c r="G291" s="9"/>
+    </row>
+    <row r="292" spans="7:7">
+      <c r="G292" s="9"/>
+    </row>
+    <row r="293" spans="7:7">
+      <c r="G293" s="9"/>
+    </row>
+    <row r="294" spans="7:7">
+      <c r="G294" s="9"/>
+    </row>
+    <row r="295" spans="7:7">
+      <c r="G295" s="9"/>
+    </row>
+    <row r="296" spans="7:7">
+      <c r="G296" s="9"/>
+    </row>
+    <row r="297" spans="7:7">
+      <c r="G297" s="9"/>
+    </row>
+    <row r="298" spans="7:7">
+      <c r="G298" s="9"/>
+    </row>
+    <row r="299" spans="7:7">
+      <c r="G299" s="9"/>
+    </row>
+    <row r="300" spans="7:7">
+      <c r="G300" s="9"/>
+    </row>
+    <row r="301" spans="7:7">
+      <c r="G301" s="9"/>
+    </row>
+    <row r="302" spans="7:7">
+      <c r="G302" s="9"/>
+    </row>
+    <row r="303" spans="7:7">
+      <c r="G303" s="9"/>
+    </row>
+    <row r="304" spans="7:7">
+      <c r="G304" s="9"/>
+    </row>
+    <row r="305" spans="7:7">
+      <c r="G305" s="9"/>
+    </row>
+    <row r="306" spans="7:7">
+      <c r="G306" s="9"/>
+    </row>
+    <row r="307" spans="7:7">
+      <c r="G307" s="9"/>
+    </row>
+    <row r="308" spans="7:7">
+      <c r="G308" s="9"/>
+    </row>
+    <row r="309" spans="7:7">
+      <c r="G309" s="9"/>
+    </row>
+    <row r="310" spans="7:7">
+      <c r="G310" s="9"/>
+    </row>
+    <row r="311" spans="7:7">
+      <c r="G311" s="9"/>
+    </row>
+    <row r="312" spans="7:7">
+      <c r="G312" s="9"/>
+    </row>
+    <row r="313" spans="7:7">
+      <c r="G313" s="9"/>
+    </row>
+    <row r="314" spans="7:7">
+      <c r="G314" s="9"/>
+    </row>
+    <row r="315" spans="7:7">
+      <c r="G315" s="9"/>
+    </row>
+    <row r="316" spans="7:7">
+      <c r="G316" s="9"/>
+    </row>
+    <row r="317" spans="7:7">
+      <c r="G317" s="9"/>
+    </row>
+    <row r="318" spans="7:7">
+      <c r="G318" s="9"/>
+    </row>
+    <row r="319" spans="7:7">
+      <c r="G319" s="9"/>
+    </row>
+    <row r="320" spans="7:7">
+      <c r="G320" s="9"/>
+    </row>
+    <row r="321" spans="7:7">
+      <c r="G321" s="9"/>
+    </row>
+    <row r="322" spans="7:7">
+      <c r="G322" s="9"/>
+    </row>
+    <row r="323" spans="7:7">
+      <c r="G323" s="9"/>
+    </row>
+    <row r="324" spans="7:7">
+      <c r="G324" s="9"/>
+    </row>
+    <row r="325" spans="7:7">
+      <c r="G325" s="9"/>
+    </row>
+    <row r="326" spans="7:7">
+      <c r="G326" s="9"/>
+    </row>
+    <row r="327" spans="7:7">
+      <c r="G327" s="9"/>
+    </row>
+    <row r="328" spans="7:7">
+      <c r="G328" s="9"/>
+    </row>
+    <row r="329" spans="7:7">
+      <c r="G329" s="9"/>
+    </row>
+    <row r="330" spans="7:7">
+      <c r="G330" s="9"/>
+    </row>
+    <row r="331" spans="7:7">
+      <c r="G331" s="9"/>
+    </row>
+    <row r="332" spans="7:7">
+      <c r="G332" s="9"/>
+    </row>
+    <row r="333" spans="7:7">
+      <c r="G333" s="9"/>
+    </row>
+    <row r="334" spans="7:7">
+      <c r="G334" s="9"/>
+    </row>
+    <row r="335" spans="7:7">
+      <c r="G335" s="9"/>
+    </row>
+    <row r="336" spans="7:7">
+      <c r="G336" s="9"/>
+    </row>
+    <row r="337" spans="7:7">
+      <c r="G337" s="9"/>
+    </row>
+    <row r="338" spans="7:7">
+      <c r="G338" s="9"/>
+    </row>
+    <row r="339" spans="7:7">
+      <c r="G339" s="9"/>
+    </row>
+    <row r="340" spans="7:7">
+      <c r="G340" s="9"/>
+    </row>
+    <row r="341" spans="7:7">
+      <c r="G341" s="9"/>
+    </row>
+    <row r="342" spans="7:7">
+      <c r="G342" s="9"/>
+    </row>
+    <row r="343" spans="7:7">
+      <c r="G343" s="9"/>
+    </row>
+    <row r="344" spans="7:7">
+      <c r="G344" s="9"/>
+    </row>
+    <row r="345" spans="7:7">
+      <c r="G345" s="9"/>
+    </row>
+    <row r="346" spans="7:7">
+      <c r="G346" s="9"/>
+    </row>
+    <row r="347" spans="7:7">
+      <c r="G347" s="9"/>
+    </row>
+    <row r="348" spans="7:7">
+      <c r="G348" s="9"/>
+    </row>
+    <row r="349" spans="7:7">
+      <c r="G349" s="9"/>
+    </row>
+    <row r="350" spans="7:7">
+      <c r="G350" s="9"/>
+    </row>
+    <row r="351" spans="7:7">
+      <c r="G351" s="9"/>
+    </row>
+    <row r="352" spans="7:7">
+      <c r="G352" s="9"/>
+    </row>
+    <row r="353" spans="7:7">
+      <c r="G353" s="9"/>
+    </row>
+    <row r="354" spans="7:7">
+      <c r="G354" s="9"/>
+    </row>
+    <row r="355" spans="7:7">
+      <c r="G355" s="9"/>
+    </row>
+    <row r="356" spans="7:7">
+      <c r="G356" s="9"/>
+    </row>
+    <row r="357" spans="7:7">
+      <c r="G357" s="9"/>
+    </row>
+    <row r="358" spans="7:7">
+      <c r="G358" s="9"/>
+    </row>
+    <row r="359" spans="7:7">
+      <c r="G359" s="9"/>
+    </row>
+    <row r="360" spans="7:7">
+      <c r="G360" s="9"/>
+    </row>
+    <row r="361" spans="7:7">
+      <c r="G361" s="9"/>
+    </row>
+    <row r="362" spans="7:7">
+      <c r="G362" s="9"/>
+    </row>
+    <row r="363" spans="7:7">
+      <c r="G363" s="9"/>
+    </row>
+    <row r="364" spans="7:7">
+      <c r="G364" s="9"/>
+    </row>
+    <row r="365" spans="7:7">
+      <c r="G365" s="9"/>
+    </row>
+    <row r="366" spans="7:7">
+      <c r="G366" s="9"/>
+    </row>
+    <row r="367" spans="7:7">
+      <c r="G367" s="9"/>
+    </row>
+    <row r="368" spans="7:7">
+      <c r="G368" s="9"/>
+    </row>
+    <row r="369" spans="7:7">
+      <c r="G369" s="9"/>
+    </row>
+    <row r="370" spans="7:7">
+      <c r="G370" s="9"/>
+    </row>
+    <row r="371" spans="7:7">
+      <c r="G371" s="9"/>
+    </row>
+    <row r="372" spans="7:7">
+      <c r="G372" s="9"/>
+    </row>
+    <row r="373" spans="7:7">
+      <c r="G373" s="9"/>
+    </row>
+    <row r="374" spans="7:7">
+      <c r="G374" s="9"/>
+    </row>
+    <row r="375" spans="7:7">
+      <c r="G375" s="9"/>
+    </row>
+    <row r="376" spans="7:7">
+      <c r="G376" s="9"/>
+    </row>
+    <row r="377" spans="7:7">
+      <c r="G377" s="9"/>
+    </row>
+    <row r="378" spans="7:7">
+      <c r="G378" s="9"/>
+    </row>
+    <row r="379" spans="7:7">
+      <c r="G379" s="9"/>
+    </row>
+    <row r="380" spans="7:7">
+      <c r="G380" s="9"/>
+    </row>
+    <row r="381" spans="7:7">
+      <c r="G381" s="9"/>
+    </row>
+    <row r="382" spans="7:7">
+      <c r="G382" s="9"/>
+    </row>
+    <row r="383" spans="7:7">
+      <c r="G383" s="9"/>
+    </row>
+    <row r="384" spans="7:7">
+      <c r="G384" s="9"/>
+    </row>
+    <row r="385" spans="7:7">
+      <c r="G385" s="9"/>
+    </row>
+    <row r="386" spans="7:7">
+      <c r="G386" s="9"/>
+    </row>
+    <row r="387" spans="7:7">
+      <c r="G387" s="9"/>
+    </row>
+    <row r="388" spans="7:7">
+      <c r="G388" s="9"/>
+    </row>
+    <row r="389" spans="7:7">
+      <c r="G389" s="9"/>
+    </row>
+    <row r="390" spans="7:7">
+      <c r="G390" s="9"/>
+    </row>
+    <row r="391" spans="7:7">
+      <c r="G391" s="9"/>
+    </row>
+    <row r="392" spans="7:7">
+      <c r="G392" s="9"/>
+    </row>
+    <row r="393" spans="7:7">
+      <c r="G393" s="9"/>
+    </row>
+    <row r="394" spans="7:7">
+      <c r="G394" s="9"/>
+    </row>
+    <row r="395" spans="7:7">
+      <c r="G395" s="9"/>
+    </row>
+    <row r="396" spans="7:7">
+      <c r="G396" s="9"/>
+    </row>
+    <row r="397" spans="7:7">
+      <c r="G397" s="9"/>
+    </row>
+    <row r="398" spans="7:7">
+      <c r="G398" s="9"/>
+    </row>
+    <row r="399" spans="7:7">
+      <c r="G399" s="9"/>
+    </row>
+    <row r="400" spans="7:7">
+      <c r="G400" s="9"/>
+    </row>
+    <row r="401" spans="7:7">
+      <c r="G401" s="9"/>
+    </row>
+    <row r="402" spans="7:7">
+      <c r="G402" s="9"/>
+    </row>
+    <row r="403" spans="7:7">
+      <c r="G403" s="9"/>
+    </row>
+    <row r="404" spans="7:7">
+      <c r="G404" s="9"/>
+    </row>
+    <row r="405" spans="7:7">
+      <c r="G405" s="9"/>
+    </row>
+    <row r="406" spans="7:7">
+      <c r="G406" s="9"/>
+    </row>
+    <row r="407" spans="7:7">
+      <c r="G407" s="9"/>
+    </row>
+    <row r="408" spans="7:7">
+      <c r="G408" s="9"/>
+    </row>
+    <row r="409" spans="7:7">
+      <c r="G409" s="9"/>
+    </row>
+    <row r="410" spans="7:7">
+      <c r="G410" s="9"/>
+    </row>
+    <row r="411" spans="7:7">
+      <c r="G411" s="9"/>
+    </row>
+    <row r="412" spans="7:7">
+      <c r="G412" s="9"/>
+    </row>
+    <row r="413" spans="7:7">
+      <c r="G413" s="9"/>
+    </row>
+    <row r="414" spans="7:7">
+      <c r="G414" s="9"/>
+    </row>
+    <row r="415" spans="7:7">
+      <c r="G415" s="9"/>
+    </row>
+    <row r="416" spans="7:7">
+      <c r="G416" s="9"/>
+    </row>
+    <row r="417" spans="7:7">
+      <c r="G417" s="9"/>
+    </row>
+    <row r="418" spans="7:7">
+      <c r="G418" s="9"/>
+    </row>
+    <row r="419" spans="7:7">
+      <c r="G419" s="9"/>
+    </row>
+    <row r="420" spans="7:7">
+      <c r="G420" s="9"/>
+    </row>
+    <row r="421" spans="7:7">
+      <c r="G421" s="9"/>
+    </row>
+    <row r="422" spans="7:7">
+      <c r="G422" s="9"/>
+    </row>
+    <row r="423" spans="7:7">
+      <c r="G423" s="9"/>
+    </row>
+    <row r="424" spans="7:7">
+      <c r="G424" s="9"/>
+    </row>
+    <row r="425" spans="7:7">
+      <c r="G425" s="9"/>
+    </row>
+    <row r="426" spans="7:7">
+      <c r="G426" s="9"/>
+    </row>
+    <row r="427" spans="7:7">
+      <c r="G427" s="9"/>
+    </row>
+    <row r="428" spans="7:7">
+      <c r="G428" s="9"/>
+    </row>
+    <row r="429" spans="7:7">
+      <c r="G429" s="9"/>
+    </row>
+    <row r="430" spans="7:7">
+      <c r="G430" s="9"/>
+    </row>
+    <row r="431" spans="7:7">
+      <c r="G431" s="9"/>
+    </row>
+    <row r="432" spans="7:7">
+      <c r="G432" s="9"/>
+    </row>
+    <row r="433" spans="7:7">
+      <c r="G433" s="9"/>
+    </row>
+    <row r="434" spans="7:7">
+      <c r="G434" s="9"/>
+    </row>
+    <row r="435" spans="7:7">
+      <c r="G435" s="9"/>
+    </row>
+    <row r="436" spans="7:7">
+      <c r="G436" s="9"/>
+    </row>
+    <row r="437" spans="7:7">
+      <c r="G437" s="9"/>
+    </row>
+    <row r="438" spans="7:7">
+      <c r="G438" s="9"/>
+    </row>
+    <row r="439" spans="7:7">
+      <c r="G439" s="9"/>
+    </row>
+    <row r="440" spans="7:7">
+      <c r="G440" s="9"/>
+    </row>
+    <row r="441" spans="7:7">
+      <c r="G441" s="9"/>
+    </row>
+    <row r="442" spans="7:7">
+      <c r="G442" s="9"/>
+    </row>
+    <row r="443" spans="7:7">
+      <c r="G443" s="9"/>
+    </row>
+    <row r="444" spans="7:7">
+      <c r="G444" s="9"/>
+    </row>
+    <row r="445" spans="7:7">
+      <c r="G445" s="9"/>
+    </row>
+    <row r="446" spans="7:7">
+      <c r="G446" s="9"/>
+    </row>
+    <row r="447" spans="7:7">
+      <c r="G447" s="9"/>
+    </row>
+    <row r="448" spans="7:7">
+      <c r="G448" s="9"/>
+    </row>
+    <row r="449" spans="7:7">
+      <c r="G449" s="9"/>
+    </row>
+    <row r="450" spans="7:7">
+      <c r="G450" s="9"/>
+    </row>
+    <row r="451" spans="7:7">
+      <c r="G451" s="9"/>
+    </row>
+    <row r="452" spans="7:7">
+      <c r="G452" s="9"/>
+    </row>
+    <row r="453" spans="7:7">
+      <c r="G453" s="9"/>
+    </row>
+    <row r="454" spans="7:7">
+      <c r="G454" s="9"/>
+    </row>
+    <row r="455" spans="7:7">
+      <c r="G455" s="9"/>
+    </row>
+    <row r="456" spans="7:7">
+      <c r="G456" s="9"/>
+    </row>
+    <row r="457" spans="7:7">
+      <c r="G457" s="9"/>
+    </row>
+    <row r="458" spans="7:7">
+      <c r="G458" s="9"/>
+    </row>
+    <row r="459" spans="7:7">
+      <c r="G459" s="9"/>
+    </row>
+    <row r="460" spans="7:7">
+      <c r="G460" s="9"/>
+    </row>
+    <row r="461" spans="7:7">
+      <c r="G461" s="9"/>
+    </row>
+    <row r="462" spans="7:7">
+      <c r="G462" s="9"/>
+    </row>
+    <row r="463" spans="7:7">
+      <c r="G463" s="9"/>
+    </row>
+    <row r="464" spans="7:7">
+      <c r="G464" s="9"/>
+    </row>
+    <row r="465" spans="7:7">
+      <c r="G465" s="9"/>
+    </row>
+    <row r="466" spans="7:7">
+      <c r="G466" s="9"/>
+    </row>
+    <row r="467" spans="7:7">
+      <c r="G467" s="9"/>
+    </row>
+    <row r="468" spans="7:7">
+      <c r="G468" s="9"/>
+    </row>
+    <row r="469" spans="7:7">
+      <c r="G469" s="9"/>
+    </row>
+    <row r="470" spans="7:7">
+      <c r="G470" s="9"/>
+    </row>
+    <row r="471" spans="7:7">
+      <c r="G471" s="9"/>
+    </row>
+    <row r="472" spans="7:7">
+      <c r="G472" s="9"/>
+    </row>
+    <row r="473" spans="7:7">
+      <c r="G473" s="9"/>
+    </row>
+    <row r="474" spans="7:7">
+      <c r="G474" s="9"/>
+    </row>
+    <row r="475" spans="7:7">
+      <c r="G475" s="9"/>
+    </row>
+    <row r="476" spans="7:7">
+      <c r="G476" s="9"/>
+    </row>
+    <row r="477" spans="7:7">
+      <c r="G477" s="9"/>
+    </row>
+    <row r="478" spans="7:7">
+      <c r="G478" s="9"/>
+    </row>
+    <row r="479" spans="7:7">
+      <c r="G479" s="9"/>
+    </row>
+    <row r="480" spans="7:7">
+      <c r="G480" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K135" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <autoFilter ref="A1:N135" xr:uid="{00000000-0001-0000-0400-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Sprint 0"/>
+        <filter val="Sprint 2"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K17">
-      <sortCondition ref="K1:K135"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A36:N53">
+      <sortCondition ref="L1:L135"/>
     </sortState>
   </autoFilter>
   <dataValidations count="7">
@@ -20751,47 +22343,92 @@
     <dataValidation type="list" allowBlank="1" sqref="F2:F200" xr:uid="{00000000-0002-0000-0400-000002000000}">
       <formula1>"Backlog,Ready,To Do,In Progress,Review,Done,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K135" xr:uid="{00000000-0002-0000-0400-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="L2:L135 M2:M17" xr:uid="{00000000-0002-0000-0400-000003000000}">
       <formula1>"PB-001,PB-002,PB-003,PB-004,PB-005,PB-006,PB-007,PB-008,PB-009,PB-010,PB-011,PB-012,PB-013,PB-014,PB-015,PB-016,PB-017,PB-018,PB-019,PB-020,PB-021,PB-022,PB-023,PB-024,PB-025,PB-026,PB-027,PB-028,PB-029,PB-030,PB-031,PB-032,PB-033,PB-034,PB-035,PB-036"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="F12:F135" xr:uid="{00000000-0002-0000-0400-000006000000}">
       <formula1>"Backlog,Ready,To Do,In Progress,Review,Done,Blocked,Moved"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G12:G135" xr:uid="{00000000-0002-0000-0400-000007000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H12:H135" xr:uid="{00000000-0002-0000-0400-000007000000}">
       <formula1>"Developer,Product Owner,Tester,Designer,DevOps"</formula1>
     </dataValidation>
-    <dataValidation type="whole" sqref="H12:H135" xr:uid="{00000000-0002-0000-0400-000008000000}">
+    <dataValidation type="whole" sqref="I12:I135" xr:uid="{00000000-0002-0000-0400-000008000000}">
       <formula1>0</formula1>
       <formula2>40</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{7F92D44F-5205-2149-B975-DFCDE5C9B7F0}"/>
+    <hyperlink ref="N3" r:id="rId2" xr:uid="{6B26BEE6-E39C-4A4F-932C-57C4679DB5AB}"/>
+    <hyperlink ref="N4:N5" r:id="rId3" display="Pull Request #2" xr:uid="{6960549B-0414-614E-BC27-118EF8902A98}"/>
+    <hyperlink ref="N6" r:id="rId4" xr:uid="{CDB635C0-C155-AE4C-A997-5F8EC0AA1C1E}"/>
+    <hyperlink ref="N7" r:id="rId5" xr:uid="{B2115D65-2215-6646-91F9-FB38B5D36ABB}"/>
+    <hyperlink ref="N8" r:id="rId6" xr:uid="{EE27927D-C3C9-9B49-B5AC-436819FA5302}"/>
+    <hyperlink ref="N9" r:id="rId7" xr:uid="{E86C9B2D-E7A2-E747-9403-2FB70C77684A}"/>
+    <hyperlink ref="N10" r:id="rId8" xr:uid="{C60BAEFE-31F6-654C-AC59-2600AF2C78BF}"/>
+    <hyperlink ref="N11:N13" r:id="rId9" display="https://github.com/dqhieuse/sport_booking_webapp/commit/9ea6710c55bd5d75ce992ff74a9f8bc98e625ef7" xr:uid="{9374657B-5171-584E-8D9D-9DED091BF4EE}"/>
+    <hyperlink ref="N14" r:id="rId10" xr:uid="{F41BA02F-3749-FE4F-B415-1C96F6CA537B}"/>
+    <hyperlink ref="N16:N17" r:id="rId11" display="https://github.com/dqhieuse/sport_booking_webapp/commit/ee452ebe7b0fe9bfb4b1f96c2503a23e0b9919da" xr:uid="{7F9D6751-138D-2C47-98B8-569E84074D1F}"/>
+    <hyperlink ref="N15" r:id="rId12" xr:uid="{3024326C-1656-594E-A949-B35D7EF95F1C}"/>
+    <hyperlink ref="N18" r:id="rId13" xr:uid="{972C7B3B-E8FB-DA40-8F2C-2FEC4A0654B0}"/>
+    <hyperlink ref="N19" r:id="rId14" xr:uid="{1B52CCB9-CF8B-D347-AE54-9EDAE3B81C8A}"/>
+    <hyperlink ref="N20" r:id="rId15" xr:uid="{97B23BBA-A7F8-0744-9B0A-2AB7359D5B0D}"/>
+    <hyperlink ref="N21" r:id="rId16" xr:uid="{5A715AC1-5EA3-AE4A-8570-CC8584E9905B}"/>
+    <hyperlink ref="N22" r:id="rId17" xr:uid="{304AFB1A-4D9C-B346-ADBB-5B148F7472C6}"/>
+    <hyperlink ref="N23:N24" r:id="rId18" display="https://github.com/dqhieuse/sport_booking_webapp/commit/7c28081b592376b5f114320c4b2b97ab7aaafcf5" xr:uid="{0949C457-399A-1F4E-AA13-A7A6AA88738A}"/>
+    <hyperlink ref="N25" r:id="rId19" xr:uid="{459C229E-046E-AF4F-8D1C-261A9AF05DD6}"/>
+    <hyperlink ref="N27" r:id="rId20" xr:uid="{F1B82A34-2A01-E140-864B-C694112EE8CA}"/>
+    <hyperlink ref="N28" r:id="rId21" xr:uid="{5A071FBD-2661-4148-B857-18440AD2DAE8}"/>
+    <hyperlink ref="N29" r:id="rId22" xr:uid="{5C4CE2C9-8535-E04C-8750-15EC6FF979CA}"/>
+    <hyperlink ref="N26" r:id="rId23" xr:uid="{D4A7C388-A18A-AB49-97D0-48E503CE2886}"/>
+    <hyperlink ref="N30" r:id="rId24" xr:uid="{826E87A7-432B-B443-82EE-044A2B1A3FAC}"/>
+    <hyperlink ref="N31" r:id="rId25" xr:uid="{D19F9E8D-2314-0F45-A877-EF3048D34838}"/>
+    <hyperlink ref="N32" r:id="rId26" xr:uid="{1A834366-22EC-3F42-AB7F-ECC74031D86D}"/>
+    <hyperlink ref="N33" r:id="rId27" xr:uid="{2C2A1686-CEAF-864E-A060-0105A0CB183A}"/>
+    <hyperlink ref="N34" r:id="rId28" xr:uid="{B282F9E2-9F28-C646-A1C5-C7962753C156}"/>
+    <hyperlink ref="N35" r:id="rId29" xr:uid="{BA879A5A-E4E3-934B-826B-66FF43BD6272}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{9559DBF6-A389-4C40-AE73-5962CA372B58}">
-            <xm:f>Lookups!$A$2</xm:f>
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{217C811A-50C3-6E4A-B7A8-DAA3E491C4A4}">
+            <xm:f>Lookups!$A$8</xm:f>
             <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
               <fill>
                 <patternFill>
-                  <bgColor theme="2"/>
+                  <bgColor rgb="FFFFC7CE"/>
                 </patternFill>
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>F2:F473</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{92255747-59BC-7847-BC4C-69D98DEC60BF}">
-            <xm:f>Lookups!$A$3</xm:f>
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{64D0E3E5-43C0-3A46-A0D7-D80846A93428}">
+            <xm:f>Lookups!$A$7</xm:f>
             <x14:dxf>
               <font>
-                <color rgb="FF7030A0"/>
+                <color rgb="FF006100"/>
               </font>
               <fill>
                 <patternFill>
-                  <bgColor rgb="FFEAE8FF"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{8A95AAF8-7E8C-3949-91B7-852351398651}">
+            <xm:f>Lookups!$A$6</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C5700"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFEB9C"/>
                 </patternFill>
               </fill>
             </x14:dxf>
@@ -20809,48 +22446,45 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{8A95AAF8-7E8C-3949-91B7-852351398651}">
-            <xm:f>Lookups!$A$6</xm:f>
+          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{92255747-59BC-7847-BC4C-69D98DEC60BF}">
+            <xm:f>Lookups!$A$3</xm:f>
             <x14:dxf>
               <font>
-                <color rgb="FF9C5700"/>
+                <color rgb="FF7030A0"/>
               </font>
               <fill>
                 <patternFill>
-                  <bgColor rgb="FFFFEB9C"/>
+                  <bgColor rgb="FFEAE8FF"/>
                 </patternFill>
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{64D0E3E5-43C0-3A46-A0D7-D80846A93428}">
-            <xm:f>Lookups!$A$7</xm:f>
+          <xm:sqref>F1:G1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{9559DBF6-A389-4C40-AE73-5962CA372B58}">
+            <xm:f>Lookups!$A$2</xm:f>
             <x14:dxf>
-              <font>
-                <color rgb="FF006100"/>
-              </font>
               <fill>
                 <patternFill>
-                  <bgColor rgb="FFC6EFCE"/>
+                  <bgColor theme="2"/>
                 </patternFill>
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{217C811A-50C3-6E4A-B7A8-DAA3E491C4A4}">
-            <xm:f>Lookups!$A$8</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FF9C0006"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>F1:F1048576</xm:sqref>
+          <xm:sqref>F2:G473 G2:G480</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B2B1BAD3-1944-AF40-849D-6D0E6B54E401}">
+          <x14:formula1>
+            <xm:f>Lookups!$I$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G509</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
     </ext>
   </extLst>
 </worksheet>
@@ -20905,7 +22539,7 @@
         <v>174</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
@@ -29111,6 +30745,7 @@
     <col min="6" max="6" width="15.1640625" customWidth="1"/>
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
     <col min="8" max="8" width="11.83203125" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="35.75" customHeight="1">
@@ -29138,7 +30773,9 @@
       <c r="H1" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="I1" s="1"/>
+      <c r="I1" s="8" t="s">
+        <v>861</v>
+      </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
@@ -29167,7 +30804,9 @@
       <c r="H2" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="I2" s="1"/>
+      <c r="I2" s="41" t="s">
+        <v>862</v>
+      </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
